--- a/Overture-Match-Suggestions/CY.xlsx
+++ b/Overture-Match-Suggestions/CY.xlsx
@@ -651,10 +651,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Αυγόρου</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -747,10 +755,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Ορμήδεια</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
@@ -843,10 +859,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Ξυλοτύμβου</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
@@ -939,10 +963,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Achna</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
@@ -1025,10 +1057,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Αγία Νάπα</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -1121,10 +1161,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Παραλίμνι</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
@@ -1211,10 +1259,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Δερύνεια</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -1301,10 +1357,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Σωτήρα</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
@@ -1391,10 +1455,18 @@
           <t>FamagustaCyprus</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Λιοπέτρι</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
@@ -1487,10 +1559,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Gazimağusa</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
@@ -1645,10 +1725,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Beyarmudu</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
@@ -1735,10 +1823,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Paşaköy</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="n"/>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
@@ -1825,10 +1921,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>İnönü</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="n"/>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
@@ -1915,10 +2019,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Akdoğan</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="n"/>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
@@ -2005,10 +2117,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Serdarlı</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
@@ -2095,10 +2215,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Vadili</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
@@ -2185,10 +2313,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Geçitkale</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
@@ -2275,10 +2411,18 @@
           <t>GazimağusaCyprus</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Tatlısu</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
@@ -2371,10 +2515,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Girne</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
@@ -2529,10 +2681,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Lapta</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
@@ -2619,10 +2779,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Alsancak</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
@@ -2709,10 +2877,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Çatalköy</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
@@ -2799,10 +2975,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Lapta</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
@@ -2889,10 +3073,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Esentepe</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
@@ -2979,10 +3171,18 @@
           <t>GirneCyprus</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="n"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Karaman</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
@@ -3075,10 +3275,18 @@
           <t>GüzelyurtCyprus</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Güzelyurt</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
@@ -3165,10 +3373,18 @@
           <t>İskeleCyprus</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>İskele</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
@@ -3321,10 +3537,18 @@
           <t>İskeleCyprus</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Mehmetçik</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
@@ -3411,10 +3635,18 @@
           <t>İskeleCyprus</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Büyükkonuk</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
@@ -3501,10 +3733,18 @@
           <t>İskeleCyprus</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Dipkarpaz</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
@@ -3663,10 +3903,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="n"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Ξυλοφάγου</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
@@ -3759,10 +4007,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Λάρνακας</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="n"/>
       <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
@@ -3857,10 +4113,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Αραδίππου</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
@@ -3947,10 +4211,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Λιβαδιών</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
@@ -4197,10 +4469,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Athienou</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
@@ -4287,10 +4567,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Κίτι</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="n"/>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
@@ -4377,10 +4665,18 @@
           <t>LarnacaCyprus</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Πύλα</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
@@ -4467,10 +4763,18 @@
           <t>LefkeCyprus</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Lefka</t>
+        </is>
+      </c>
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
@@ -4563,10 +4867,18 @@
           <t>LefkoşaCyprus</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Kuzey Lefkoşa</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
@@ -4659,10 +4971,18 @@
           <t>LefkoşaCyprus</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Gönyeli</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="n"/>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
@@ -4749,10 +5069,18 @@
           <t>LefkoşaCyprus</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Değirmenlik</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="n"/>
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
@@ -4839,10 +5167,18 @@
           <t>LefkoşaCyprus</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Alayköy</t>
+        </is>
+      </c>
       <c r="Q49" s="2" t="n"/>
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
@@ -4929,10 +5265,18 @@
           <t>LefkoşaCyprus</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Akıncılar</t>
+        </is>
+      </c>
       <c r="Q50" s="2" t="n"/>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
@@ -5025,10 +5369,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
-      <c r="P51" s="2" t="n"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Λεμεσός</t>
+        </is>
+      </c>
       <c r="Q51" s="2" t="n"/>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
@@ -5123,10 +5475,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="n"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Κάτω Πολεμιδίων</t>
+        </is>
+      </c>
       <c r="Q52" s="2" t="n"/>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
@@ -5219,10 +5579,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Germasogeia</t>
+        </is>
+      </c>
       <c r="Q53" s="2" t="n"/>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
@@ -5315,10 +5683,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Agios Athanasios</t>
+        </is>
+      </c>
       <c r="Q54" s="2" t="n"/>
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
@@ -5411,10 +5787,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
-      <c r="P55" s="2" t="n"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Μέσα Γειτονιάς</t>
+        </is>
+      </c>
       <c r="Q55" s="2" t="n"/>
       <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
@@ -5507,10 +5891,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Ύψωνας</t>
+        </is>
+      </c>
       <c r="Q56" s="2" t="n"/>
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
@@ -5603,10 +5995,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="n"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Κολόσσι</t>
+        </is>
+      </c>
       <c r="Q57" s="2" t="n"/>
       <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
@@ -5699,10 +6099,18 @@
           <t>LimassolCyprus</t>
         </is>
       </c>
-      <c r="M58" s="4" t="n"/>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
-      <c r="P58" s="4" t="n"/>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>Mouttayiaka</t>
+        </is>
+      </c>
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
@@ -5795,10 +6203,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
-      <c r="P59" s="2" t="n"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Strovolos</t>
+        </is>
+      </c>
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
@@ -5891,10 +6307,20 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="n"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
       <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
@@ -5989,10 +6415,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Λακατάμεια</t>
+        </is>
+      </c>
       <c r="Q61" s="2" t="n"/>
       <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
@@ -6085,10 +6519,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M62" s="3" t="n"/>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N62" s="3" t="n"/>
       <c r="O62" s="3" t="n"/>
-      <c r="P62" s="3" t="n"/>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Αγλαντζιά</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="n"/>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3" t="n"/>
@@ -6171,10 +6613,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M63" s="3" t="n"/>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N63" s="3" t="n"/>
       <c r="O63" s="3" t="n"/>
-      <c r="P63" s="3" t="n"/>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>Έγκωμη</t>
+        </is>
+      </c>
       <c r="Q63" s="3" t="n"/>
       <c r="R63" s="3" t="n"/>
       <c r="S63" s="3" t="n"/>
@@ -6257,10 +6707,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Latsia</t>
+        </is>
+      </c>
       <c r="Q64" s="2" t="n"/>
       <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
@@ -6353,10 +6811,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="n"/>
       <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Geri</t>
+        </is>
+      </c>
       <c r="Q65" s="2" t="n"/>
       <c r="R65" s="2" t="n"/>
       <c r="S65" s="2" t="n"/>
@@ -6449,10 +6915,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Tseri</t>
+        </is>
+      </c>
       <c r="Q66" s="2" t="n"/>
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
@@ -6619,10 +7093,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="n"/>
       <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Dali</t>
+        </is>
+      </c>
       <c r="Q68" s="2" t="n"/>
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
@@ -6709,10 +7191,18 @@
           <t>NicosiaCyprus</t>
         </is>
       </c>
-      <c r="M69" s="2" t="n"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="n"/>
       <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Κοκκινοτριμιθιά</t>
+        </is>
+      </c>
       <c r="Q69" s="2" t="n"/>
       <c r="R69" s="2" t="n"/>
       <c r="S69" s="2" t="n"/>
@@ -6805,10 +7295,20 @@
           <t>PaphosCyprus</t>
         </is>
       </c>
-      <c r="M70" s="2" t="n"/>
-      <c r="N70" s="2" t="n"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="n"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Paphos</t>
+        </is>
+      </c>
       <c r="Q70" s="2" t="n"/>
       <c r="R70" s="2" t="n"/>
       <c r="S70" s="2" t="n"/>
@@ -6897,10 +7397,18 @@
           <t>PaphosCyprus</t>
         </is>
       </c>
-      <c r="M71" s="2" t="n"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="n"/>
       <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Γεροσκήπου</t>
+        </is>
+      </c>
       <c r="Q71" s="2" t="n"/>
       <c r="R71" s="2" t="n"/>
       <c r="S71" s="2" t="n"/>
@@ -6987,10 +7495,18 @@
           <t>PaphosCyprus</t>
         </is>
       </c>
-      <c r="M72" s="2" t="n"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="n"/>
       <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Πέγεια</t>
+        </is>
+      </c>
       <c r="Q72" s="2" t="n"/>
       <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
@@ -7077,10 +7593,18 @@
           <t>PaphosCyprus</t>
         </is>
       </c>
-      <c r="M73" s="5" t="n"/>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N73" s="5" t="n"/>
       <c r="O73" s="5" t="n"/>
-      <c r="P73" s="5" t="n"/>
+      <c r="P73" s="5" t="inlineStr">
+        <is>
+          <t>Hlorakas</t>
+        </is>
+      </c>
       <c r="Q73" s="5" t="n"/>
       <c r="R73" s="5" t="n"/>
       <c r="S73" s="5" t="n"/>
@@ -7167,10 +7691,18 @@
           <t>PaphosCyprus</t>
         </is>
       </c>
-      <c r="M74" s="2" t="n"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="n"/>
       <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="n"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="Q74" s="2" t="n"/>
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
@@ -7331,10 +7863,18 @@
       <c r="L76" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M76" s="2" t="n"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="n"/>
-      <c r="P76" s="2" t="n"/>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Τραχώνι</t>
+        </is>
+      </c>
       <c r="Q76" s="2" t="n"/>
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
@@ -7415,10 +7955,18 @@
       <c r="L77" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M77" s="2" t="n"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Φρέναρος</t>
+        </is>
+      </c>
       <c r="Q77" s="2" t="n"/>
       <c r="R77" s="2" t="n"/>
       <c r="S77" s="2" t="n"/>
@@ -7619,10 +8167,18 @@
       <c r="L80" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M80" s="2" t="n"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="n"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>Επισκοπή</t>
+        </is>
+      </c>
       <c r="Q80" s="2" t="n"/>
       <c r="R80" s="2" t="n"/>
       <c r="S80" s="2" t="n"/>
@@ -7703,10 +8259,18 @@
       <c r="L81" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M81" s="2" t="n"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="n"/>
       <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Πύλα</t>
+        </is>
+      </c>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="n"/>
       <c r="S81" s="2" t="n"/>
@@ -7787,10 +8351,18 @@
       <c r="L82" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M82" s="2" t="n"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="n"/>
       <c r="O82" s="2" t="n"/>
-      <c r="P82" s="2" t="n"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Parekklisia</t>
+        </is>
+      </c>
       <c r="Q82" s="2" t="n"/>
       <c r="R82" s="2" t="n"/>
       <c r="S82" s="2" t="n"/>
@@ -7871,10 +8443,18 @@
       <c r="L83" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M83" s="2" t="n"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="2" t="n"/>
-      <c r="P83" s="2" t="n"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Πάνω Πολεμιδίων</t>
+        </is>
+      </c>
       <c r="Q83" s="2" t="n"/>
       <c r="R83" s="2" t="n"/>
       <c r="S83" s="2" t="n"/>
@@ -8015,10 +8595,18 @@
       <c r="L85" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M85" s="2" t="n"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="n"/>
       <c r="O85" s="2" t="n"/>
-      <c r="P85" s="2" t="n"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Ερήμη</t>
+        </is>
+      </c>
       <c r="Q85" s="2" t="n"/>
       <c r="R85" s="2" t="n"/>
       <c r="S85" s="2" t="n"/>
@@ -8099,10 +8687,18 @@
       <c r="L86" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M86" s="2" t="n"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Lythrodontas</t>
+        </is>
+      </c>
       <c r="Q86" s="2" t="n"/>
       <c r="R86" s="2" t="n"/>
       <c r="S86" s="2" t="n"/>
@@ -8183,10 +8779,18 @@
       <c r="L87" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M87" s="2" t="n"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="2" t="n"/>
-      <c r="P87" s="2" t="n"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Akaki</t>
+        </is>
+      </c>
       <c r="Q87" s="2" t="n"/>
       <c r="R87" s="2" t="n"/>
       <c r="S87" s="2" t="n"/>
@@ -8267,10 +8871,18 @@
       <c r="L88" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M88" s="2" t="n"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="2" t="n"/>
-      <c r="P88" s="2" t="n"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Tala</t>
+        </is>
+      </c>
       <c r="Q88" s="2" t="n"/>
       <c r="R88" s="2" t="n"/>
       <c r="S88" s="2" t="n"/>
@@ -8351,10 +8963,18 @@
       <c r="L89" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M89" s="2" t="n"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="2" t="n"/>
-      <c r="P89" s="2" t="n"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Pyrgos</t>
+        </is>
+      </c>
       <c r="Q89" s="2" t="n"/>
       <c r="R89" s="2" t="n"/>
       <c r="S89" s="2" t="n"/>
@@ -8435,10 +9055,18 @@
       <c r="L90" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M90" s="2" t="n"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="n"/>
       <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="n"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Pano Deftera</t>
+        </is>
+      </c>
       <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="n"/>
       <c r="S90" s="2" t="n"/>
@@ -8519,10 +9147,18 @@
       <c r="L91" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M91" s="2" t="n"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="2" t="n"/>
-      <c r="P91" s="2" t="n"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Pera Chorio</t>
+        </is>
+      </c>
       <c r="Q91" s="2" t="n"/>
       <c r="R91" s="2" t="n"/>
       <c r="S91" s="2" t="n"/>
@@ -8603,10 +9239,18 @@
       <c r="L92" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M92" s="2" t="n"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="2" t="n"/>
-      <c r="P92" s="2" t="n"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Lympia</t>
+        </is>
+      </c>
       <c r="Q92" s="2" t="n"/>
       <c r="R92" s="2" t="n"/>
       <c r="S92" s="2" t="n"/>
@@ -8687,10 +9331,18 @@
       <c r="L93" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M93" s="2" t="n"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="2" t="n"/>
-      <c r="P93" s="2" t="n"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Agia Varvara</t>
+        </is>
+      </c>
       <c r="Q93" s="2" t="n"/>
       <c r="R93" s="2" t="n"/>
       <c r="S93" s="2" t="n"/>
@@ -8771,10 +9423,18 @@
       <c r="L94" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M94" s="2" t="n"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="2" t="n"/>
-      <c r="P94" s="2" t="n"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>Konia</t>
+        </is>
+      </c>
       <c r="Q94" s="2" t="n"/>
       <c r="R94" s="2" t="n"/>
       <c r="S94" s="2" t="n"/>
@@ -8855,10 +9515,18 @@
       <c r="L95" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M95" s="2" t="n"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="2" t="n"/>
-      <c r="P95" s="2" t="n"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Kissonerga</t>
+        </is>
+      </c>
       <c r="Q95" s="2" t="n"/>
       <c r="R95" s="2" t="n"/>
       <c r="S95" s="2" t="n"/>
@@ -8939,10 +9607,18 @@
       <c r="L96" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M96" s="2" t="n"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="2" t="n"/>
-      <c r="P96" s="2" t="n"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Περιστερώνα</t>
+        </is>
+      </c>
       <c r="Q96" s="2" t="n"/>
       <c r="R96" s="2" t="n"/>
       <c r="S96" s="2" t="n"/>
@@ -9023,10 +9699,18 @@
       <c r="L97" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M97" s="2" t="n"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="2" t="n"/>
-      <c r="P97" s="2" t="n"/>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Astromeritis</t>
+        </is>
+      </c>
       <c r="Q97" s="2" t="n"/>
       <c r="R97" s="2" t="n"/>
       <c r="S97" s="2" t="n"/>
@@ -9107,10 +9791,18 @@
       <c r="L98" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M98" s="2" t="n"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="2" t="n"/>
-      <c r="P98" s="2" t="n"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Kato Deftera</t>
+        </is>
+      </c>
       <c r="Q98" s="2" t="n"/>
       <c r="R98" s="2" t="n"/>
       <c r="S98" s="2" t="n"/>
@@ -9191,10 +9883,18 @@
       <c r="L99" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M99" s="2" t="n"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="2" t="n"/>
-      <c r="P99" s="2" t="n"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>Nisou</t>
+        </is>
+      </c>
       <c r="Q99" s="2" t="n"/>
       <c r="R99" s="2" t="n"/>
       <c r="S99" s="2" t="n"/>
@@ -9275,10 +9975,18 @@
       <c r="L100" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M100" s="2" t="n"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="n"/>
       <c r="O100" s="2" t="n"/>
-      <c r="P100" s="2" t="n"/>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>Palodeia</t>
+        </is>
+      </c>
       <c r="Q100" s="2" t="n"/>
       <c r="R100" s="2" t="n"/>
       <c r="S100" s="2" t="n"/>
@@ -9359,10 +10067,18 @@
       <c r="L101" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M101" s="2" t="n"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="n"/>
-      <c r="P101" s="2" t="n"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Kornos</t>
+        </is>
+      </c>
       <c r="Q101" s="2" t="n"/>
       <c r="R101" s="2" t="n"/>
       <c r="S101" s="2" t="n"/>
@@ -9443,10 +10159,18 @@
       <c r="L102" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M102" s="2" t="n"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="2" t="n"/>
-      <c r="P102" s="2" t="n"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Πισσούρι</t>
+        </is>
+      </c>
       <c r="Q102" s="2" t="n"/>
       <c r="R102" s="2" t="n"/>
       <c r="S102" s="2" t="n"/>
@@ -9527,10 +10251,18 @@
       <c r="L103" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M103" s="2" t="n"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="2" t="n"/>
-      <c r="P103" s="2" t="n"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Agioi Trimithias</t>
+        </is>
+      </c>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="n"/>
       <c r="S103" s="2" t="n"/>
@@ -9611,10 +10343,18 @@
       <c r="L104" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M104" s="2" t="n"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Ergates</t>
+        </is>
+      </c>
       <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="n"/>
       <c r="S104" s="2" t="n"/>
@@ -9695,10 +10435,18 @@
       <c r="L105" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M105" s="2" t="n"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="2" t="n"/>
-      <c r="P105" s="2" t="n"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Psimolofou</t>
+        </is>
+      </c>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="n"/>
       <c r="S105" s="2" t="n"/>
@@ -9779,10 +10527,18 @@
       <c r="L106" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M106" s="2" t="n"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="n"/>
       <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>Mammari</t>
+        </is>
+      </c>
       <c r="Q106" s="2" t="n"/>
       <c r="R106" s="2" t="n"/>
       <c r="S106" s="2" t="n"/>
@@ -9863,10 +10619,18 @@
       <c r="L107" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M107" s="2" t="n"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>Acheritou</t>
+        </is>
+      </c>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
@@ -9947,10 +10711,18 @@
       <c r="L108" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M108" s="2" t="n"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="2" t="n"/>
-      <c r="P108" s="2" t="n"/>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>Klirou</t>
+        </is>
+      </c>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="n"/>
       <c r="S108" s="2" t="n"/>
@@ -10031,10 +10803,18 @@
       <c r="L109" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M109" s="2" t="n"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N109" s="2" t="n"/>
       <c r="O109" s="2" t="n"/>
-      <c r="P109" s="2" t="n"/>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>Mesogi</t>
+        </is>
+      </c>
       <c r="Q109" s="2" t="n"/>
       <c r="R109" s="2" t="n"/>
       <c r="S109" s="2" t="n"/>
@@ -10115,10 +10895,18 @@
       <c r="L110" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M110" s="2" t="n"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N110" s="2" t="n"/>
       <c r="O110" s="2" t="n"/>
-      <c r="P110" s="2" t="n"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>Τερσεφάνου</t>
+        </is>
+      </c>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
       <c r="S110" s="2" t="n"/>
@@ -10199,10 +10987,18 @@
       <c r="L111" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M111" s="2" t="n"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>Συνοικισμός Ανθούπολης</t>
+        </is>
+      </c>
       <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="n"/>
       <c r="S111" s="2" t="n"/>
@@ -10283,10 +11079,18 @@
       <c r="L112" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M112" s="2" t="n"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="2" t="n"/>
-      <c r="P112" s="2" t="n"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>Alampra</t>
+        </is>
+      </c>
       <c r="Q112" s="2" t="n"/>
       <c r="R112" s="2" t="n"/>
       <c r="S112" s="2" t="n"/>
@@ -10367,10 +11171,18 @@
       <c r="L113" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M113" s="2" t="n"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="2" t="n"/>
-      <c r="P113" s="2" t="n"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>Alethriko</t>
+        </is>
+      </c>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="n"/>
       <c r="S113" s="2" t="n"/>
@@ -10451,10 +11263,18 @@
       <c r="L114" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M114" s="2" t="n"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="2" t="n"/>
-      <c r="P114" s="2" t="n"/>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>Anageia</t>
+        </is>
+      </c>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
@@ -10595,10 +11415,18 @@
       <c r="L116" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M116" s="2" t="n"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="2" t="n"/>
-      <c r="P116" s="2" t="n"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>Mosfiloti</t>
+        </is>
+      </c>
       <c r="Q116" s="2" t="n"/>
       <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
@@ -10679,10 +11507,18 @@
       <c r="L117" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M117" s="2" t="n"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="2" t="n"/>
-      <c r="P117" s="2" t="n"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>Pera</t>
+        </is>
+      </c>
       <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="n"/>
       <c r="S117" s="2" t="n"/>
@@ -10763,10 +11599,18 @@
       <c r="L118" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M118" s="2" t="n"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N118" s="2" t="n"/>
       <c r="O118" s="2" t="n"/>
-      <c r="P118" s="2" t="n"/>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>Κυπερούντα</t>
+        </is>
+      </c>
       <c r="Q118" s="2" t="n"/>
       <c r="R118" s="2" t="n"/>
       <c r="S118" s="2" t="n"/>
@@ -10847,10 +11691,18 @@
       <c r="L119" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M119" s="2" t="n"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="2" t="n"/>
-      <c r="P119" s="2" t="n"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>Kofinou</t>
+        </is>
+      </c>
       <c r="Q119" s="2" t="n"/>
       <c r="R119" s="2" t="n"/>
       <c r="S119" s="2" t="n"/>
@@ -10931,10 +11783,18 @@
       <c r="L120" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M120" s="2" t="n"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N120" s="2" t="n"/>
       <c r="O120" s="2" t="n"/>
-      <c r="P120" s="2" t="n"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>Psevdas</t>
+        </is>
+      </c>
       <c r="Q120" s="2" t="n"/>
       <c r="R120" s="2" t="n"/>
       <c r="S120" s="2" t="n"/>
@@ -11015,10 +11875,18 @@
       <c r="L121" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M121" s="2" t="n"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="n"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>Arediou</t>
+        </is>
+      </c>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="2" t="n"/>
       <c r="S121" s="2" t="n"/>
@@ -11099,10 +11967,18 @@
       <c r="L122" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M122" s="2" t="n"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="2" t="n"/>
-      <c r="P122" s="2" t="n"/>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>Souni-Zanakia</t>
+        </is>
+      </c>
       <c r="Q122" s="2" t="n"/>
       <c r="R122" s="2" t="n"/>
       <c r="S122" s="2" t="n"/>
@@ -11183,10 +12059,18 @@
       <c r="L123" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M123" s="2" t="n"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="2" t="n"/>
-      <c r="P123" s="2" t="n"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>Kakopetria</t>
+        </is>
+      </c>
       <c r="Q123" s="2" t="n"/>
       <c r="R123" s="2" t="n"/>
       <c r="S123" s="2" t="n"/>
@@ -11267,10 +12151,18 @@
       <c r="L124" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M124" s="2" t="n"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="2" t="n"/>
-      <c r="P124" s="2" t="n"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>Anglisides</t>
+        </is>
+      </c>
       <c r="Q124" s="2" t="n"/>
       <c r="R124" s="2" t="n"/>
       <c r="S124" s="2" t="n"/>
@@ -11351,10 +12243,18 @@
       <c r="L125" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M125" s="2" t="n"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="2" t="n"/>
-      <c r="P125" s="2" t="n"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>Kouklia</t>
+        </is>
+      </c>
       <c r="Q125" s="2" t="n"/>
       <c r="R125" s="2" t="n"/>
       <c r="S125" s="2" t="n"/>
@@ -11435,10 +12335,18 @@
       <c r="L126" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M126" s="2" t="n"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>Troulloi</t>
+        </is>
+      </c>
       <c r="Q126" s="2" t="n"/>
       <c r="R126" s="2" t="n"/>
       <c r="S126" s="2" t="n"/>
@@ -11519,10 +12427,18 @@
       <c r="L127" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M127" s="2" t="n"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="2" t="n"/>
-      <c r="P127" s="2" t="n"/>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>Tsada</t>
+        </is>
+      </c>
       <c r="Q127" s="2" t="n"/>
       <c r="R127" s="2" t="n"/>
       <c r="S127" s="2" t="n"/>
@@ -11603,10 +12519,18 @@
       <c r="L128" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M128" s="2" t="n"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="2" t="n"/>
-      <c r="P128" s="2" t="n"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>Tremithousa</t>
+        </is>
+      </c>
       <c r="Q128" s="2" t="n"/>
       <c r="R128" s="2" t="n"/>
       <c r="S128" s="2" t="n"/>
@@ -11687,10 +12611,18 @@
       <c r="L129" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M129" s="2" t="n"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="2" t="n"/>
-      <c r="P129" s="2" t="n"/>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>Mazotos</t>
+        </is>
+      </c>
       <c r="Q129" s="2" t="n"/>
       <c r="R129" s="2" t="n"/>
       <c r="S129" s="2" t="n"/>
@@ -11771,10 +12703,18 @@
       <c r="L130" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M130" s="2" t="n"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="2" t="n"/>
-      <c r="P130" s="2" t="n"/>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>Mandria</t>
+        </is>
+      </c>
       <c r="Q130" s="2" t="n"/>
       <c r="R130" s="2" t="n"/>
       <c r="S130" s="2" t="n"/>
@@ -11855,10 +12795,18 @@
       <c r="L131" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M131" s="2" t="n"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="2" t="n"/>
-      <c r="P131" s="2" t="n"/>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>Αργάκα</t>
+        </is>
+      </c>
       <c r="Q131" s="2" t="n"/>
       <c r="R131" s="2" t="n"/>
       <c r="S131" s="2" t="n"/>
@@ -11939,10 +12887,18 @@
       <c r="L132" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M132" s="2" t="n"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="2" t="n"/>
-      <c r="P132" s="2" t="n"/>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>Timi</t>
+        </is>
+      </c>
       <c r="Q132" s="2" t="n"/>
       <c r="R132" s="2" t="n"/>
       <c r="S132" s="2" t="n"/>
@@ -12023,10 +12979,18 @@
       <c r="L133" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M133" s="2" t="n"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="2" t="n"/>
-      <c r="P133" s="2" t="n"/>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>Meniko</t>
+        </is>
+      </c>
       <c r="Q133" s="2" t="n"/>
       <c r="R133" s="2" t="n"/>
       <c r="S133" s="2" t="n"/>
@@ -12107,10 +13071,18 @@
       <c r="L134" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M134" s="2" t="n"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="2" t="n"/>
-      <c r="P134" s="2" t="n"/>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>Πελένδρι</t>
+        </is>
+      </c>
       <c r="Q134" s="2" t="n"/>
       <c r="R134" s="2" t="n"/>
       <c r="S134" s="2" t="n"/>
@@ -12191,10 +13163,18 @@
       <c r="L135" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M135" s="2" t="n"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="2" t="n"/>
-      <c r="P135" s="2" t="n"/>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>Anarita</t>
+        </is>
+      </c>
       <c r="Q135" s="2" t="n"/>
       <c r="R135" s="2" t="n"/>
       <c r="S135" s="2" t="n"/>
@@ -12275,10 +13255,18 @@
       <c r="L136" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M136" s="2" t="n"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="2" t="n"/>
-      <c r="P136" s="2" t="n"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Moni</t>
+        </is>
+      </c>
       <c r="Q136" s="2" t="n"/>
       <c r="R136" s="2" t="n"/>
       <c r="S136" s="2" t="n"/>
@@ -12359,10 +13347,18 @@
       <c r="L137" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M137" s="2" t="n"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="2" t="n"/>
-      <c r="P137" s="2" t="n"/>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>Akrotiri</t>
+        </is>
+      </c>
       <c r="Q137" s="2" t="n"/>
       <c r="R137" s="2" t="n"/>
       <c r="S137" s="2" t="n"/>
@@ -12443,10 +13439,18 @@
       <c r="L138" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M138" s="2" t="n"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="2" t="n"/>
-      <c r="P138" s="2" t="n"/>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>Κάτω Πύργος</t>
+        </is>
+      </c>
       <c r="Q138" s="2" t="n"/>
       <c r="R138" s="2" t="n"/>
       <c r="S138" s="2" t="n"/>
@@ -12527,10 +13531,18 @@
       <c r="L139" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M139" s="2" t="n"/>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="2" t="n"/>
-      <c r="P139" s="2" t="n"/>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>Pano Kivides</t>
+        </is>
+      </c>
       <c r="Q139" s="2" t="n"/>
       <c r="R139" s="2" t="n"/>
       <c r="S139" s="2" t="n"/>
@@ -12611,10 +13623,18 @@
       <c r="L140" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M140" s="2" t="n"/>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="2" t="n"/>
-      <c r="P140" s="2" t="n"/>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>Ασώματος</t>
+        </is>
+      </c>
       <c r="Q140" s="2" t="n"/>
       <c r="R140" s="2" t="n"/>
       <c r="S140" s="2" t="n"/>
@@ -12695,10 +13715,18 @@
       <c r="L141" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M141" s="2" t="n"/>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="2" t="n"/>
-      <c r="P141" s="2" t="n"/>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>Kalavasos</t>
+        </is>
+      </c>
       <c r="Q141" s="2" t="n"/>
       <c r="R141" s="2" t="n"/>
       <c r="S141" s="2" t="n"/>
@@ -12779,10 +13807,18 @@
       <c r="L142" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M142" s="2" t="n"/>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="2" t="n"/>
-      <c r="P142" s="2" t="n"/>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>Polemi</t>
+        </is>
+      </c>
       <c r="Q142" s="2" t="n"/>
       <c r="R142" s="2" t="n"/>
       <c r="S142" s="2" t="n"/>
@@ -12863,10 +13899,18 @@
       <c r="L143" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M143" s="2" t="n"/>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="2" t="n"/>
-      <c r="P143" s="2" t="n"/>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>Pyrga</t>
+        </is>
+      </c>
       <c r="Q143" s="2" t="n"/>
       <c r="R143" s="2" t="n"/>
       <c r="S143" s="2" t="n"/>
@@ -12947,10 +13991,18 @@
       <c r="L144" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M144" s="2" t="n"/>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="2" t="n"/>
-      <c r="P144" s="2" t="n"/>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>Pano Lefkara</t>
+        </is>
+      </c>
       <c r="Q144" s="2" t="n"/>
       <c r="R144" s="2" t="n"/>
       <c r="S144" s="2" t="n"/>
@@ -13031,10 +14083,18 @@
       <c r="L145" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M145" s="2" t="n"/>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N145" s="2" t="n"/>
       <c r="O145" s="2" t="n"/>
-      <c r="P145" s="2" t="n"/>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>Mesa Chorio</t>
+        </is>
+      </c>
       <c r="Q145" s="2" t="n"/>
       <c r="R145" s="2" t="n"/>
       <c r="S145" s="2" t="n"/>
@@ -13115,10 +14175,18 @@
       <c r="L146" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M146" s="2" t="n"/>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="2" t="n"/>
-      <c r="P146" s="2" t="n"/>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>Evrychou</t>
+        </is>
+      </c>
       <c r="Q146" s="2" t="n"/>
       <c r="R146" s="2" t="n"/>
       <c r="S146" s="2" t="n"/>
@@ -13199,10 +14267,18 @@
       <c r="L147" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M147" s="2" t="n"/>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="2" t="n"/>
-      <c r="P147" s="2" t="n"/>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>Pachna</t>
+        </is>
+      </c>
       <c r="Q147" s="2" t="n"/>
       <c r="R147" s="2" t="n"/>
       <c r="S147" s="2" t="n"/>
@@ -13283,10 +14359,18 @@
       <c r="L148" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M148" s="2" t="n"/>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="2" t="n"/>
-      <c r="P148" s="2" t="n"/>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>Αγρός</t>
+        </is>
+      </c>
       <c r="Q148" s="2" t="n"/>
       <c r="R148" s="2" t="n"/>
       <c r="S148" s="2" t="n"/>
@@ -13367,10 +14451,18 @@
       <c r="L149" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M149" s="2" t="n"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="2" t="n"/>
-      <c r="P149" s="2" t="n"/>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>Sia</t>
+        </is>
+      </c>
       <c r="Q149" s="2" t="n"/>
       <c r="R149" s="2" t="n"/>
       <c r="S149" s="2" t="n"/>
@@ -13451,10 +14543,18 @@
       <c r="L150" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M150" s="2" t="n"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="2" t="n"/>
-      <c r="P150" s="2" t="n"/>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>Anafotida</t>
+        </is>
+      </c>
       <c r="Q150" s="2" t="n"/>
       <c r="R150" s="2" t="n"/>
       <c r="S150" s="2" t="n"/>
@@ -13535,10 +14635,18 @@
       <c r="L151" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M151" s="2" t="n"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="2" t="n"/>
-      <c r="P151" s="2" t="n"/>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>Giolou</t>
+        </is>
+      </c>
       <c r="Q151" s="2" t="n"/>
       <c r="R151" s="2" t="n"/>
       <c r="S151" s="2" t="n"/>
@@ -13619,10 +14727,18 @@
       <c r="L152" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M152" s="2" t="n"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="2" t="n"/>
-      <c r="P152" s="2" t="n"/>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>Monagroulli</t>
+        </is>
+      </c>
       <c r="Q152" s="2" t="n"/>
       <c r="R152" s="2" t="n"/>
       <c r="S152" s="2" t="n"/>
@@ -13703,10 +14819,18 @@
       <c r="L153" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M153" s="2" t="n"/>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="2" t="n"/>
-      <c r="P153" s="2" t="n"/>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>Mitsero</t>
+        </is>
+      </c>
       <c r="Q153" s="2" t="n"/>
       <c r="R153" s="2" t="n"/>
       <c r="S153" s="2" t="n"/>
@@ -13787,10 +14911,18 @@
       <c r="L154" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M154" s="2" t="n"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="2" t="n"/>
-      <c r="P154" s="2" t="n"/>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>Πεντάκωμο</t>
+        </is>
+      </c>
       <c r="Q154" s="2" t="n"/>
       <c r="R154" s="2" t="n"/>
       <c r="S154" s="2" t="n"/>
@@ -13871,10 +15003,18 @@
       <c r="L155" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M155" s="2" t="n"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="2" t="n"/>
-      <c r="P155" s="2" t="n"/>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>Choirokoitia</t>
+        </is>
+      </c>
       <c r="Q155" s="2" t="n"/>
       <c r="R155" s="2" t="n"/>
       <c r="S155" s="2" t="n"/>
@@ -14015,10 +15155,18 @@
       <c r="L157" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M157" s="2" t="n"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="2" t="n"/>
-      <c r="P157" s="2" t="n"/>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>Maroni</t>
+        </is>
+      </c>
       <c r="Q157" s="2" t="n"/>
       <c r="R157" s="2" t="n"/>
       <c r="S157" s="2" t="n"/>
@@ -14159,10 +15307,18 @@
       <c r="L159" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M159" s="2" t="n"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N159" s="2" t="n"/>
       <c r="O159" s="2" t="n"/>
-      <c r="P159" s="2" t="n"/>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>Αγιος Θεόδωρος</t>
+        </is>
+      </c>
       <c r="Q159" s="2" t="n"/>
       <c r="R159" s="2" t="n"/>
       <c r="S159" s="2" t="n"/>
@@ -14243,10 +15399,18 @@
       <c r="L160" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M160" s="2" t="n"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N160" s="2" t="n"/>
       <c r="O160" s="2" t="n"/>
-      <c r="P160" s="2" t="n"/>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>Paramytha</t>
+        </is>
+      </c>
       <c r="Q160" s="2" t="n"/>
       <c r="R160" s="2" t="n"/>
       <c r="S160" s="2" t="n"/>
@@ -14387,10 +15551,18 @@
       <c r="L162" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M162" s="2" t="n"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="2" t="n"/>
-      <c r="P162" s="2" t="n"/>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>Mathiatis</t>
+        </is>
+      </c>
       <c r="Q162" s="2" t="n"/>
       <c r="R162" s="2" t="n"/>
       <c r="S162" s="2" t="n"/>
@@ -14471,10 +15643,18 @@
       <c r="L163" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M163" s="2" t="n"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="2" t="n"/>
-      <c r="P163" s="2" t="n"/>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>Zygi</t>
+        </is>
+      </c>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="n"/>
       <c r="S163" s="2" t="n"/>
@@ -14555,10 +15735,18 @@
       <c r="L164" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M164" s="2" t="n"/>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N164" s="2" t="n"/>
       <c r="O164" s="2" t="n"/>
-      <c r="P164" s="2" t="n"/>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>Armou</t>
+        </is>
+      </c>
       <c r="Q164" s="2" t="n"/>
       <c r="R164" s="2" t="n"/>
       <c r="S164" s="2" t="n"/>
@@ -14639,10 +15827,18 @@
       <c r="L165" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M165" s="2" t="n"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="2" t="n"/>
-      <c r="P165" s="2" t="n"/>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>Apesia</t>
+        </is>
+      </c>
       <c r="Q165" s="2" t="n"/>
       <c r="R165" s="2" t="n"/>
       <c r="S165" s="2" t="n"/>
@@ -14723,10 +15919,18 @@
       <c r="L166" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M166" s="2" t="n"/>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="2" t="n"/>
-      <c r="P166" s="2" t="n"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>Stroumpi</t>
+        </is>
+      </c>
       <c r="Q166" s="2" t="n"/>
       <c r="R166" s="2" t="n"/>
       <c r="S166" s="2" t="n"/>
@@ -14867,10 +16071,18 @@
       <c r="L168" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M168" s="2" t="n"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N168" s="2" t="n"/>
       <c r="O168" s="2" t="n"/>
-      <c r="P168" s="2" t="n"/>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>Potamia</t>
+        </is>
+      </c>
       <c r="Q168" s="2" t="n"/>
       <c r="R168" s="2" t="n"/>
       <c r="S168" s="2" t="n"/>
@@ -14951,10 +16163,18 @@
       <c r="L169" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M169" s="2" t="n"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N169" s="2" t="n"/>
       <c r="O169" s="2" t="n"/>
-      <c r="P169" s="2" t="n"/>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>Galata</t>
+        </is>
+      </c>
       <c r="Q169" s="2" t="n"/>
       <c r="R169" s="2" t="n"/>
       <c r="S169" s="2" t="n"/>
@@ -15035,10 +16255,18 @@
       <c r="L170" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M170" s="2" t="n"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="2" t="n"/>
-      <c r="P170" s="2" t="n"/>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>Kapedes</t>
+        </is>
+      </c>
       <c r="Q170" s="2" t="n"/>
       <c r="R170" s="2" t="n"/>
       <c r="S170" s="2" t="n"/>
@@ -15119,10 +16347,18 @@
       <c r="L171" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M171" s="2" t="n"/>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="2" t="n"/>
-      <c r="P171" s="2" t="n"/>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>Αυδήμου</t>
+        </is>
+      </c>
       <c r="Q171" s="2" t="n"/>
       <c r="R171" s="2" t="n"/>
       <c r="S171" s="2" t="n"/>
@@ -15203,10 +16439,18 @@
       <c r="L172" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M172" s="2" t="n"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="2" t="n"/>
-      <c r="P172" s="2" t="n"/>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>Episkopeio</t>
+        </is>
+      </c>
       <c r="Q172" s="2" t="n"/>
       <c r="R172" s="2" t="n"/>
       <c r="S172" s="2" t="n"/>
@@ -15287,10 +16531,18 @@
       <c r="L173" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M173" s="2" t="n"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="2" t="n"/>
-      <c r="P173" s="2" t="n"/>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>Koili</t>
+        </is>
+      </c>
       <c r="Q173" s="2" t="n"/>
       <c r="R173" s="2" t="n"/>
       <c r="S173" s="2" t="n"/>
@@ -15371,10 +16623,18 @@
       <c r="L174" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M174" s="2" t="n"/>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="2" t="n"/>
-      <c r="P174" s="2" t="n"/>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>Potami</t>
+        </is>
+      </c>
       <c r="Q174" s="2" t="n"/>
       <c r="R174" s="2" t="n"/>
       <c r="S174" s="2" t="n"/>
@@ -15455,10 +16715,18 @@
       <c r="L175" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M175" s="2" t="n"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N175" s="2" t="n"/>
       <c r="O175" s="2" t="n"/>
-      <c r="P175" s="2" t="n"/>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>Analiontas</t>
+        </is>
+      </c>
       <c r="Q175" s="2" t="n"/>
       <c r="R175" s="2" t="n"/>
       <c r="S175" s="2" t="n"/>
@@ -15539,10 +16807,18 @@
       <c r="L176" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M176" s="2" t="n"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="2" t="n"/>
-      <c r="P176" s="2" t="n"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>Kampia</t>
+        </is>
+      </c>
       <c r="Q176" s="2" t="n"/>
       <c r="R176" s="2" t="n"/>
       <c r="S176" s="2" t="n"/>
@@ -15623,10 +16899,18 @@
       <c r="L177" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M177" s="2" t="n"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="2" t="n"/>
-      <c r="P177" s="2" t="n"/>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>Agrokipia</t>
+        </is>
+      </c>
       <c r="Q177" s="2" t="n"/>
       <c r="R177" s="2" t="n"/>
       <c r="S177" s="2" t="n"/>
@@ -15707,10 +16991,18 @@
       <c r="L178" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M178" s="2" t="n"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N178" s="2" t="n"/>
       <c r="O178" s="2" t="n"/>
-      <c r="P178" s="2" t="n"/>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>Νέο Χωριό</t>
+        </is>
+      </c>
       <c r="Q178" s="2" t="n"/>
       <c r="R178" s="2" t="n"/>
       <c r="S178" s="2" t="n"/>
@@ -15791,10 +17083,18 @@
       <c r="L179" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M179" s="2" t="n"/>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N179" s="2" t="n"/>
       <c r="O179" s="2" t="n"/>
-      <c r="P179" s="2" t="n"/>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>Akrounta</t>
+        </is>
+      </c>
       <c r="Q179" s="2" t="n"/>
       <c r="R179" s="2" t="n"/>
       <c r="S179" s="2" t="n"/>
@@ -15875,10 +17175,18 @@
       <c r="L180" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M180" s="2" t="n"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="2" t="n"/>
-      <c r="P180" s="2" t="n"/>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>Deneia</t>
+        </is>
+      </c>
       <c r="Q180" s="2" t="n"/>
       <c r="R180" s="2" t="n"/>
       <c r="S180" s="2" t="n"/>
@@ -15959,10 +17267,18 @@
       <c r="L181" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M181" s="2" t="n"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="2" t="n"/>
-      <c r="P181" s="2" t="n"/>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>Malounta</t>
+        </is>
+      </c>
       <c r="Q181" s="2" t="n"/>
       <c r="R181" s="2" t="n"/>
       <c r="S181" s="2" t="n"/>
@@ -16043,10 +17359,18 @@
       <c r="L182" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M182" s="2" t="n"/>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N182" s="2" t="n"/>
       <c r="O182" s="2" t="n"/>
-      <c r="P182" s="2" t="n"/>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>Orounta</t>
+        </is>
+      </c>
       <c r="Q182" s="2" t="n"/>
       <c r="R182" s="2" t="n"/>
       <c r="S182" s="2" t="n"/>
@@ -16187,10 +17511,18 @@
       <c r="L184" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M184" s="2" t="n"/>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N184" s="2" t="n"/>
       <c r="O184" s="2" t="n"/>
-      <c r="P184" s="2" t="n"/>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>Korakou</t>
+        </is>
+      </c>
       <c r="Q184" s="2" t="n"/>
       <c r="R184" s="2" t="n"/>
       <c r="S184" s="2" t="n"/>
@@ -16331,10 +17663,18 @@
       <c r="L186" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M186" s="2" t="n"/>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="2" t="n"/>
-      <c r="P186" s="2" t="n"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>Temvria</t>
+        </is>
+      </c>
       <c r="Q186" s="2" t="n"/>
       <c r="R186" s="2" t="n"/>
       <c r="S186" s="2" t="n"/>
@@ -16415,10 +17755,18 @@
       <c r="L187" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M187" s="2" t="n"/>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="2" t="n"/>
-      <c r="P187" s="2" t="n"/>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>Agios Ioannis</t>
+        </is>
+      </c>
       <c r="Q187" s="2" t="n"/>
       <c r="R187" s="2" t="n"/>
       <c r="S187" s="2" t="n"/>
@@ -16499,10 +17847,18 @@
       <c r="L188" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M188" s="2" t="n"/>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="2" t="n"/>
-      <c r="P188" s="2" t="n"/>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>Δρούσεια</t>
+        </is>
+      </c>
       <c r="Q188" s="2" t="n"/>
       <c r="R188" s="2" t="n"/>
       <c r="S188" s="2" t="n"/>
@@ -16583,10 +17939,18 @@
       <c r="L189" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M189" s="2" t="n"/>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="2" t="n"/>
-      <c r="P189" s="2" t="n"/>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>Ασγάτα</t>
+        </is>
+      </c>
       <c r="Q189" s="2" t="n"/>
       <c r="R189" s="2" t="n"/>
       <c r="S189" s="2" t="n"/>
@@ -16727,10 +18091,18 @@
       <c r="L191" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M191" s="2" t="n"/>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="2" t="n"/>
-      <c r="P191" s="2" t="n"/>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>Lempa</t>
+        </is>
+      </c>
       <c r="Q191" s="2" t="n"/>
       <c r="R191" s="2" t="n"/>
       <c r="S191" s="2" t="n"/>
@@ -16811,10 +18183,18 @@
       <c r="L192" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M192" s="2" t="n"/>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="2" t="n"/>
-      <c r="P192" s="2" t="n"/>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>Πωμός</t>
+        </is>
+      </c>
       <c r="Q192" s="2" t="n"/>
       <c r="R192" s="2" t="n"/>
       <c r="S192" s="2" t="n"/>
@@ -16895,10 +18275,18 @@
       <c r="L193" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M193" s="2" t="n"/>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="2" t="n"/>
-      <c r="P193" s="2" t="n"/>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>Agios Epifanios</t>
+        </is>
+      </c>
       <c r="Q193" s="2" t="n"/>
       <c r="R193" s="2" t="n"/>
       <c r="S193" s="2" t="n"/>
@@ -16979,10 +18367,18 @@
       <c r="L194" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M194" s="2" t="n"/>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="2" t="n"/>
-      <c r="P194" s="2" t="n"/>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>Farmakas</t>
+        </is>
+      </c>
       <c r="Q194" s="2" t="n"/>
       <c r="R194" s="2" t="n"/>
       <c r="S194" s="2" t="n"/>
@@ -17063,10 +18459,18 @@
       <c r="L195" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M195" s="2" t="n"/>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="2" t="n"/>
-      <c r="P195" s="2" t="n"/>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>Nikitari</t>
+        </is>
+      </c>
       <c r="Q195" s="2" t="n"/>
       <c r="R195" s="2" t="n"/>
       <c r="S195" s="2" t="n"/>
@@ -17147,10 +18551,18 @@
       <c r="L196" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M196" s="2" t="n"/>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="2" t="n"/>
-      <c r="P196" s="2" t="n"/>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>Tochni</t>
+        </is>
+      </c>
       <c r="Q196" s="2" t="n"/>
       <c r="R196" s="2" t="n"/>
       <c r="S196" s="2" t="n"/>
@@ -17231,10 +18643,18 @@
       <c r="L197" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M197" s="2" t="n"/>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N197" s="2" t="n"/>
       <c r="O197" s="2" t="n"/>
-      <c r="P197" s="2" t="n"/>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>Agia Marinouda</t>
+        </is>
+      </c>
       <c r="Q197" s="2" t="n"/>
       <c r="R197" s="2" t="n"/>
       <c r="S197" s="2" t="n"/>
@@ -17315,10 +18735,18 @@
       <c r="L198" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M198" s="2" t="n"/>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N198" s="2" t="n"/>
       <c r="O198" s="2" t="n"/>
-      <c r="P198" s="2" t="n"/>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>Politiko</t>
+        </is>
+      </c>
       <c r="Q198" s="2" t="n"/>
       <c r="R198" s="2" t="n"/>
       <c r="S198" s="2" t="n"/>
@@ -17459,10 +18887,18 @@
       <c r="L200" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M200" s="2" t="n"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="2" t="n"/>
-      <c r="P200" s="2" t="n"/>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>Kantou</t>
+        </is>
+      </c>
       <c r="Q200" s="2" t="n"/>
       <c r="R200" s="2" t="n"/>
       <c r="S200" s="2" t="n"/>
@@ -17543,10 +18979,18 @@
       <c r="L201" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M201" s="2" t="n"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N201" s="2" t="n"/>
       <c r="O201" s="2" t="n"/>
-      <c r="P201" s="2" t="n"/>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>Skarinou</t>
+        </is>
+      </c>
       <c r="Q201" s="2" t="n"/>
       <c r="R201" s="2" t="n"/>
       <c r="S201" s="2" t="n"/>
@@ -17627,10 +19071,18 @@
       <c r="L202" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M202" s="2" t="n"/>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N202" s="2" t="n"/>
       <c r="O202" s="2" t="n"/>
-      <c r="P202" s="2" t="n"/>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>Agia Anna</t>
+        </is>
+      </c>
       <c r="Q202" s="2" t="n"/>
       <c r="R202" s="2" t="n"/>
       <c r="S202" s="2" t="n"/>
@@ -17711,10 +19163,18 @@
       <c r="L203" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M203" s="2" t="n"/>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N203" s="2" t="n"/>
       <c r="O203" s="2" t="n"/>
-      <c r="P203" s="2" t="n"/>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>Klavdia</t>
+        </is>
+      </c>
       <c r="Q203" s="2" t="n"/>
       <c r="R203" s="2" t="n"/>
       <c r="S203" s="2" t="n"/>
@@ -17795,10 +19255,18 @@
       <c r="L204" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M204" s="2" t="n"/>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N204" s="2" t="n"/>
       <c r="O204" s="2" t="n"/>
-      <c r="P204" s="2" t="n"/>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>Κελλιά</t>
+        </is>
+      </c>
       <c r="Q204" s="2" t="n"/>
       <c r="R204" s="2" t="n"/>
       <c r="S204" s="2" t="n"/>
@@ -17879,10 +19347,18 @@
       <c r="L205" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M205" s="2" t="n"/>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N205" s="2" t="n"/>
       <c r="O205" s="2" t="n"/>
-      <c r="P205" s="2" t="n"/>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>Pano Panagia</t>
+        </is>
+      </c>
       <c r="Q205" s="2" t="n"/>
       <c r="R205" s="2" t="n"/>
       <c r="S205" s="2" t="n"/>
@@ -17963,10 +19439,18 @@
       <c r="L206" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M206" s="2" t="n"/>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="2" t="n"/>
-      <c r="P206" s="2" t="n"/>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>Kathikas</t>
+        </is>
+      </c>
       <c r="Q206" s="2" t="n"/>
       <c r="R206" s="2" t="n"/>
       <c r="S206" s="2" t="n"/>
@@ -18047,10 +19531,18 @@
       <c r="L207" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M207" s="2" t="n"/>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N207" s="2" t="n"/>
       <c r="O207" s="2" t="n"/>
-      <c r="P207" s="2" t="n"/>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>Laneia</t>
+        </is>
+      </c>
       <c r="Q207" s="2" t="n"/>
       <c r="R207" s="2" t="n"/>
       <c r="S207" s="2" t="n"/>
@@ -18131,10 +19623,18 @@
       <c r="L208" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M208" s="2" t="n"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N208" s="2" t="n"/>
       <c r="O208" s="2" t="n"/>
-      <c r="P208" s="2" t="n"/>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>Λουβαράς</t>
+        </is>
+      </c>
       <c r="Q208" s="2" t="n"/>
       <c r="R208" s="2" t="n"/>
       <c r="S208" s="2" t="n"/>
@@ -18215,10 +19715,18 @@
       <c r="L209" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M209" s="2" t="n"/>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N209" s="2" t="n"/>
       <c r="O209" s="2" t="n"/>
-      <c r="P209" s="2" t="n"/>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>Trimiklini</t>
+        </is>
+      </c>
       <c r="Q209" s="2" t="n"/>
       <c r="R209" s="2" t="n"/>
       <c r="S209" s="2" t="n"/>
@@ -18299,10 +19807,18 @@
       <c r="L210" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M210" s="2" t="n"/>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="2" t="n"/>
-      <c r="P210" s="2" t="n"/>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>Esentepe</t>
+        </is>
+      </c>
       <c r="Q210" s="2" t="n"/>
       <c r="R210" s="2" t="n"/>
       <c r="S210" s="2" t="n"/>
@@ -18383,10 +19899,18 @@
       <c r="L211" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M211" s="2" t="n"/>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N211" s="2" t="n"/>
       <c r="O211" s="2" t="n"/>
-      <c r="P211" s="2" t="n"/>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>Spitali</t>
+        </is>
+      </c>
       <c r="Q211" s="2" t="n"/>
       <c r="R211" s="2" t="n"/>
       <c r="S211" s="2" t="n"/>
@@ -18467,10 +19991,18 @@
       <c r="L212" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M212" s="2" t="n"/>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="2" t="n"/>
-      <c r="P212" s="2" t="n"/>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Φοινιού</t>
+        </is>
+      </c>
       <c r="Q212" s="2" t="n"/>
       <c r="R212" s="2" t="n"/>
       <c r="S212" s="2" t="n"/>
@@ -18551,10 +20083,18 @@
       <c r="L213" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M213" s="2" t="n"/>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="2" t="n"/>
-      <c r="P213" s="2" t="n"/>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>Kallepeia</t>
+        </is>
+      </c>
       <c r="Q213" s="2" t="n"/>
       <c r="R213" s="2" t="n"/>
       <c r="S213" s="2" t="n"/>
@@ -18635,10 +20175,18 @@
       <c r="L214" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M214" s="2" t="n"/>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N214" s="2" t="n"/>
       <c r="O214" s="2" t="n"/>
-      <c r="P214" s="2" t="n"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>Omodos</t>
+        </is>
+      </c>
       <c r="Q214" s="2" t="n"/>
       <c r="R214" s="2" t="n"/>
       <c r="S214" s="2" t="n"/>
@@ -18719,10 +20267,18 @@
       <c r="L215" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M215" s="2" t="n"/>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N215" s="2" t="n"/>
       <c r="O215" s="2" t="n"/>
-      <c r="P215" s="2" t="n"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>Vyzakia</t>
+        </is>
+      </c>
       <c r="Q215" s="2" t="n"/>
       <c r="R215" s="2" t="n"/>
       <c r="S215" s="2" t="n"/>
@@ -18803,10 +20359,18 @@
       <c r="L216" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M216" s="2" t="n"/>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="2" t="n"/>
-      <c r="P216" s="2" t="n"/>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>Μονιάτης</t>
+        </is>
+      </c>
       <c r="Q216" s="2" t="n"/>
       <c r="R216" s="2" t="n"/>
       <c r="S216" s="2" t="n"/>
@@ -18887,10 +20451,18 @@
       <c r="L217" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M217" s="2" t="n"/>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N217" s="2" t="n"/>
       <c r="O217" s="2" t="n"/>
-      <c r="P217" s="2" t="n"/>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>Anogyra</t>
+        </is>
+      </c>
       <c r="Q217" s="2" t="n"/>
       <c r="R217" s="2" t="n"/>
       <c r="S217" s="2" t="n"/>
@@ -18971,10 +20543,18 @@
       <c r="L218" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M218" s="2" t="n"/>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N218" s="2" t="n"/>
       <c r="O218" s="2" t="n"/>
-      <c r="P218" s="2" t="n"/>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>Marathounta</t>
+        </is>
+      </c>
       <c r="Q218" s="2" t="n"/>
       <c r="R218" s="2" t="n"/>
       <c r="S218" s="2" t="n"/>
@@ -19055,10 +20635,18 @@
       <c r="L219" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M219" s="2" t="n"/>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="2" t="n"/>
-      <c r="P219" s="2" t="n"/>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>Alaminos</t>
+        </is>
+      </c>
       <c r="Q219" s="2" t="n"/>
       <c r="R219" s="2" t="n"/>
       <c r="S219" s="2" t="n"/>
@@ -19139,10 +20727,18 @@
       <c r="L220" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M220" s="2" t="n"/>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="2" t="n"/>
-      <c r="P220" s="2" t="n"/>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>Ineia</t>
+        </is>
+      </c>
       <c r="Q220" s="2" t="n"/>
       <c r="R220" s="2" t="n"/>
       <c r="S220" s="2" t="n"/>
@@ -19223,10 +20819,18 @@
       <c r="L221" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M221" s="2" t="n"/>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N221" s="2" t="n"/>
       <c r="O221" s="2" t="n"/>
-      <c r="P221" s="2" t="n"/>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>Επταγώνια</t>
+        </is>
+      </c>
       <c r="Q221" s="2" t="n"/>
       <c r="R221" s="2" t="n"/>
       <c r="S221" s="2" t="n"/>
@@ -19307,10 +20911,18 @@
       <c r="L222" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M222" s="2" t="n"/>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N222" s="2" t="n"/>
       <c r="O222" s="2" t="n"/>
-      <c r="P222" s="2" t="n"/>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>Κελλάκι</t>
+        </is>
+      </c>
       <c r="Q222" s="2" t="n"/>
       <c r="R222" s="2" t="n"/>
       <c r="S222" s="2" t="n"/>
@@ -19391,10 +21003,18 @@
       <c r="L223" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M223" s="2" t="n"/>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N223" s="2" t="n"/>
       <c r="O223" s="2" t="n"/>
-      <c r="P223" s="2" t="n"/>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>Agios Ioannis</t>
+        </is>
+      </c>
       <c r="Q223" s="2" t="n"/>
       <c r="R223" s="2" t="n"/>
       <c r="S223" s="2" t="n"/>
@@ -19475,10 +21095,18 @@
       <c r="L224" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M224" s="2" t="n"/>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N224" s="2" t="n"/>
       <c r="O224" s="2" t="n"/>
-      <c r="P224" s="2" t="n"/>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>Limnatis</t>
+        </is>
+      </c>
       <c r="Q224" s="2" t="n"/>
       <c r="R224" s="2" t="n"/>
       <c r="S224" s="2" t="n"/>
@@ -19559,10 +21187,18 @@
       <c r="L225" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M225" s="2" t="n"/>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N225" s="2" t="n"/>
       <c r="O225" s="2" t="n"/>
-      <c r="P225" s="2" t="n"/>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>Psematismenos</t>
+        </is>
+      </c>
       <c r="Q225" s="2" t="n"/>
       <c r="R225" s="2" t="n"/>
       <c r="S225" s="2" t="n"/>
@@ -19643,10 +21279,18 @@
       <c r="L226" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M226" s="2" t="n"/>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N226" s="2" t="n"/>
       <c r="O226" s="2" t="n"/>
-      <c r="P226" s="2" t="n"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>Kato Moni</t>
+        </is>
+      </c>
       <c r="Q226" s="2" t="n"/>
       <c r="R226" s="2" t="n"/>
       <c r="S226" s="2" t="n"/>
@@ -19727,10 +21371,18 @@
       <c r="L227" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M227" s="2" t="n"/>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N227" s="2" t="n"/>
       <c r="O227" s="2" t="n"/>
-      <c r="P227" s="2" t="n"/>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>Αρακαπάς</t>
+        </is>
+      </c>
       <c r="Q227" s="2" t="n"/>
       <c r="R227" s="2" t="n"/>
       <c r="S227" s="2" t="n"/>
@@ -19811,10 +21463,18 @@
       <c r="L228" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M228" s="2" t="n"/>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N228" s="2" t="n"/>
       <c r="O228" s="2" t="n"/>
-      <c r="P228" s="2" t="n"/>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>Περιστερώνα</t>
+        </is>
+      </c>
       <c r="Q228" s="2" t="n"/>
       <c r="R228" s="2" t="n"/>
       <c r="S228" s="2" t="n"/>
@@ -19895,10 +21555,18 @@
       <c r="L229" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M229" s="2" t="n"/>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N229" s="2" t="n"/>
       <c r="O229" s="2" t="n"/>
-      <c r="P229" s="2" t="n"/>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>Alassa</t>
+        </is>
+      </c>
       <c r="Q229" s="2" t="n"/>
       <c r="R229" s="2" t="n"/>
       <c r="S229" s="2" t="n"/>
@@ -19979,10 +21647,18 @@
       <c r="L230" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M230" s="2" t="n"/>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N230" s="2" t="n"/>
       <c r="O230" s="2" t="n"/>
-      <c r="P230" s="2" t="n"/>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>Korfi</t>
+        </is>
+      </c>
       <c r="Q230" s="2" t="n"/>
       <c r="R230" s="2" t="n"/>
       <c r="S230" s="2" t="n"/>
@@ -20063,10 +21739,18 @@
       <c r="L231" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M231" s="2" t="n"/>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N231" s="2" t="n"/>
       <c r="O231" s="2" t="n"/>
-      <c r="P231" s="2" t="n"/>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>Kivisili</t>
+        </is>
+      </c>
       <c r="Q231" s="2" t="n"/>
       <c r="R231" s="2" t="n"/>
       <c r="S231" s="2" t="n"/>
@@ -20147,10 +21831,18 @@
       <c r="L232" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M232" s="2" t="n"/>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N232" s="2" t="n"/>
       <c r="O232" s="2" t="n"/>
-      <c r="P232" s="2" t="n"/>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>Avdellero</t>
+        </is>
+      </c>
       <c r="Q232" s="2" t="n"/>
       <c r="R232" s="2" t="n"/>
       <c r="S232" s="2" t="n"/>
@@ -20231,10 +21923,18 @@
       <c r="L233" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M233" s="2" t="n"/>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N233" s="2" t="n"/>
       <c r="O233" s="2" t="n"/>
-      <c r="P233" s="2" t="n"/>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>Dörtyol</t>
+        </is>
+      </c>
       <c r="Q233" s="2" t="n"/>
       <c r="R233" s="2" t="n"/>
       <c r="S233" s="2" t="n"/>
@@ -20315,10 +22015,18 @@
       <c r="L234" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M234" s="2" t="n"/>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N234" s="2" t="n"/>
       <c r="O234" s="2" t="n"/>
-      <c r="P234" s="2" t="n"/>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>Choletria</t>
+        </is>
+      </c>
       <c r="Q234" s="2" t="n"/>
       <c r="R234" s="2" t="n"/>
       <c r="S234" s="2" t="n"/>
@@ -20399,10 +22107,18 @@
       <c r="L235" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M235" s="2" t="n"/>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N235" s="2" t="n"/>
       <c r="O235" s="2" t="n"/>
-      <c r="P235" s="2" t="n"/>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>Αψιού</t>
+        </is>
+      </c>
       <c r="Q235" s="2" t="n"/>
       <c r="R235" s="2" t="n"/>
       <c r="S235" s="2" t="n"/>
@@ -20483,10 +22199,18 @@
       <c r="L236" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M236" s="2" t="n"/>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N236" s="2" t="n"/>
       <c r="O236" s="2" t="n"/>
-      <c r="P236" s="2" t="n"/>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>Letymvou</t>
+        </is>
+      </c>
       <c r="Q236" s="2" t="n"/>
       <c r="R236" s="2" t="n"/>
       <c r="S236" s="2" t="n"/>
@@ -20567,10 +22291,18 @@
       <c r="L237" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M237" s="2" t="n"/>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N237" s="2" t="n"/>
       <c r="O237" s="2" t="n"/>
-      <c r="P237" s="2" t="n"/>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>Sinaoros</t>
+        </is>
+      </c>
       <c r="Q237" s="2" t="n"/>
       <c r="R237" s="2" t="n"/>
       <c r="S237" s="2" t="n"/>
@@ -20651,10 +22383,18 @@
       <c r="L238" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M238" s="2" t="n"/>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N238" s="2" t="n"/>
       <c r="O238" s="2" t="n"/>
-      <c r="P238" s="2" t="n"/>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>Σωτήρα</t>
+        </is>
+      </c>
       <c r="Q238" s="2" t="n"/>
       <c r="R238" s="2" t="n"/>
       <c r="S238" s="2" t="n"/>
@@ -20735,10 +22475,18 @@
       <c r="L239" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M239" s="2" t="n"/>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N239" s="2" t="n"/>
       <c r="O239" s="2" t="n"/>
-      <c r="P239" s="2" t="n"/>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>Γουδί</t>
+        </is>
+      </c>
       <c r="Q239" s="2" t="n"/>
       <c r="R239" s="2" t="n"/>
       <c r="S239" s="2" t="n"/>
@@ -20819,10 +22567,18 @@
       <c r="L240" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M240" s="2" t="n"/>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N240" s="2" t="n"/>
       <c r="O240" s="2" t="n"/>
-      <c r="P240" s="2" t="n"/>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>Παραμάλι</t>
+        </is>
+      </c>
       <c r="Q240" s="2" t="n"/>
       <c r="R240" s="2" t="n"/>
       <c r="S240" s="2" t="n"/>
@@ -20903,10 +22659,18 @@
       <c r="L241" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M241" s="2" t="n"/>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N241" s="2" t="n"/>
       <c r="O241" s="2" t="n"/>
-      <c r="P241" s="2" t="n"/>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>Flasou</t>
+        </is>
+      </c>
       <c r="Q241" s="2" t="n"/>
       <c r="R241" s="2" t="n"/>
       <c r="S241" s="2" t="n"/>
@@ -20987,10 +22751,18 @@
       <c r="L242" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M242" s="2" t="n"/>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N242" s="2" t="n"/>
       <c r="O242" s="2" t="n"/>
-      <c r="P242" s="2" t="n"/>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>Armenochori</t>
+        </is>
+      </c>
       <c r="Q242" s="2" t="n"/>
       <c r="R242" s="2" t="n"/>
       <c r="S242" s="2" t="n"/>
@@ -21071,10 +22843,18 @@
       <c r="L243" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M243" s="2" t="n"/>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N243" s="2" t="n"/>
       <c r="O243" s="2" t="n"/>
-      <c r="P243" s="2" t="n"/>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>Beyarmudu</t>
+        </is>
+      </c>
       <c r="Q243" s="2" t="n"/>
       <c r="R243" s="2" t="n"/>
       <c r="S243" s="2" t="n"/>
@@ -21155,10 +22935,18 @@
       <c r="L244" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M244" s="2" t="n"/>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N244" s="2" t="n"/>
       <c r="O244" s="2" t="n"/>
-      <c r="P244" s="2" t="n"/>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>Simou</t>
+        </is>
+      </c>
       <c r="Q244" s="2" t="n"/>
       <c r="R244" s="2" t="n"/>
       <c r="S244" s="2" t="n"/>
@@ -21239,10 +23027,18 @@
       <c r="L245" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M245" s="2" t="n"/>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N245" s="2" t="n"/>
       <c r="O245" s="2" t="n"/>
-      <c r="P245" s="2" t="n"/>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>Agios Therapon</t>
+        </is>
+      </c>
       <c r="Q245" s="2" t="n"/>
       <c r="R245" s="2" t="n"/>
       <c r="S245" s="2" t="n"/>
@@ -21323,10 +23119,18 @@
       <c r="L246" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M246" s="2" t="n"/>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N246" s="2" t="n"/>
       <c r="O246" s="2" t="n"/>
-      <c r="P246" s="2" t="n"/>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>Επισκοπή</t>
+        </is>
+      </c>
       <c r="Q246" s="2" t="n"/>
       <c r="R246" s="2" t="n"/>
       <c r="S246" s="2" t="n"/>
@@ -21407,10 +23211,18 @@
       <c r="L247" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M247" s="2" t="n"/>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="2" t="n"/>
-      <c r="P247" s="2" t="n"/>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>Μαθηκολώνη</t>
+        </is>
+      </c>
       <c r="Q247" s="2" t="n"/>
       <c r="R247" s="2" t="n"/>
       <c r="S247" s="2" t="n"/>
@@ -21491,10 +23303,18 @@
       <c r="L248" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M248" s="2" t="n"/>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="2" t="n"/>
-      <c r="P248" s="2" t="n"/>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>Odou</t>
+        </is>
+      </c>
       <c r="Q248" s="2" t="n"/>
       <c r="R248" s="2" t="n"/>
       <c r="S248" s="2" t="n"/>
@@ -21575,10 +23395,18 @@
       <c r="L249" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M249" s="2" t="n"/>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="2" t="n"/>
-      <c r="P249" s="2" t="n"/>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>Kalopanagiotis</t>
+        </is>
+      </c>
       <c r="Q249" s="2" t="n"/>
       <c r="R249" s="2" t="n"/>
       <c r="S249" s="2" t="n"/>
@@ -21659,10 +23487,18 @@
       <c r="L250" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M250" s="2" t="n"/>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="2" t="n"/>
-      <c r="P250" s="2" t="n"/>
+      <c r="P250" s="2" t="inlineStr">
+        <is>
+          <t>Monagri</t>
+        </is>
+      </c>
       <c r="Q250" s="2" t="n"/>
       <c r="R250" s="2" t="n"/>
       <c r="S250" s="2" t="n"/>
@@ -21743,10 +23579,18 @@
       <c r="L251" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M251" s="2" t="n"/>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N251" s="2" t="n"/>
       <c r="O251" s="2" t="n"/>
-      <c r="P251" s="2" t="n"/>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>Πάνω Πλάτρες</t>
+        </is>
+      </c>
       <c r="Q251" s="2" t="n"/>
       <c r="R251" s="2" t="n"/>
       <c r="S251" s="2" t="n"/>
@@ -21827,10 +23671,18 @@
       <c r="L252" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M252" s="2" t="n"/>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="2" t="n"/>
-      <c r="P252" s="2" t="n"/>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>Gourri</t>
+        </is>
+      </c>
       <c r="Q252" s="2" t="n"/>
       <c r="R252" s="2" t="n"/>
       <c r="S252" s="2" t="n"/>
@@ -21911,10 +23763,18 @@
       <c r="L253" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M253" s="2" t="n"/>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="2" t="n"/>
-      <c r="P253" s="2" t="n"/>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>Salamiou</t>
+        </is>
+      </c>
       <c r="Q253" s="2" t="n"/>
       <c r="R253" s="2" t="n"/>
       <c r="S253" s="2" t="n"/>
@@ -22055,10 +23915,18 @@
       <c r="L255" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M255" s="2" t="n"/>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N255" s="2" t="n"/>
       <c r="O255" s="2" t="n"/>
-      <c r="P255" s="2" t="n"/>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>Διερώνα</t>
+        </is>
+      </c>
       <c r="Q255" s="2" t="n"/>
       <c r="R255" s="2" t="n"/>
       <c r="S255" s="2" t="n"/>
@@ -22139,10 +24007,18 @@
       <c r="L256" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M256" s="2" t="n"/>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N256" s="2" t="n"/>
       <c r="O256" s="2" t="n"/>
-      <c r="P256" s="2" t="n"/>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>Ora</t>
+        </is>
+      </c>
       <c r="Q256" s="2" t="n"/>
       <c r="R256" s="2" t="n"/>
       <c r="S256" s="2" t="n"/>
@@ -22223,10 +24099,18 @@
       <c r="L257" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M257" s="2" t="n"/>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="2" t="n"/>
-      <c r="P257" s="2" t="n"/>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>Agia Varvara</t>
+        </is>
+      </c>
       <c r="Q257" s="2" t="n"/>
       <c r="R257" s="2" t="n"/>
       <c r="S257" s="2" t="n"/>
@@ -22367,10 +24251,18 @@
       <c r="L259" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M259" s="2" t="n"/>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N259" s="2" t="n"/>
       <c r="O259" s="2" t="n"/>
-      <c r="P259" s="2" t="n"/>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>Αμίαντος</t>
+        </is>
+      </c>
       <c r="Q259" s="2" t="n"/>
       <c r="R259" s="2" t="n"/>
       <c r="S259" s="2" t="n"/>
@@ -22451,10 +24343,18 @@
       <c r="L260" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M260" s="2" t="n"/>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="2" t="n"/>
-      <c r="P260" s="2" t="n"/>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>Yiğitler</t>
+        </is>
+      </c>
       <c r="Q260" s="2" t="n"/>
       <c r="R260" s="2" t="n"/>
       <c r="S260" s="2" t="n"/>
@@ -22535,10 +24435,18 @@
       <c r="L261" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M261" s="2" t="n"/>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="2" t="n"/>
-      <c r="P261" s="2" t="n"/>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>Koilani</t>
+        </is>
+      </c>
       <c r="Q261" s="2" t="n"/>
       <c r="R261" s="2" t="n"/>
       <c r="S261" s="2" t="n"/>
@@ -22619,10 +24527,18 @@
       <c r="L262" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M262" s="2" t="n"/>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="2" t="n"/>
-      <c r="P262" s="2" t="n"/>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>Kaliana</t>
+        </is>
+      </c>
       <c r="Q262" s="2" t="n"/>
       <c r="R262" s="2" t="n"/>
       <c r="S262" s="2" t="n"/>
@@ -22703,10 +24619,18 @@
       <c r="L263" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M263" s="2" t="n"/>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N263" s="2" t="n"/>
       <c r="O263" s="2" t="n"/>
-      <c r="P263" s="2" t="n"/>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>Lysos</t>
+        </is>
+      </c>
       <c r="Q263" s="2" t="n"/>
       <c r="R263" s="2" t="n"/>
       <c r="S263" s="2" t="n"/>
@@ -22787,10 +24711,18 @@
       <c r="L264" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M264" s="2" t="n"/>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="2" t="n"/>
-      <c r="P264" s="2" t="n"/>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>Αγιος Κωνσταντίνος</t>
+        </is>
+      </c>
       <c r="Q264" s="2" t="n"/>
       <c r="R264" s="2" t="n"/>
       <c r="S264" s="2" t="n"/>
@@ -22871,10 +24803,18 @@
       <c r="L265" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M265" s="2" t="n"/>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="2" t="n"/>
-      <c r="P265" s="2" t="n"/>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>Kampos</t>
+        </is>
+      </c>
       <c r="Q265" s="2" t="n"/>
       <c r="R265" s="2" t="n"/>
       <c r="S265" s="2" t="n"/>
@@ -22955,10 +24895,18 @@
       <c r="L266" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M266" s="2" t="n"/>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N266" s="2" t="n"/>
       <c r="O266" s="2" t="n"/>
-      <c r="P266" s="2" t="n"/>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>Kotsiatis</t>
+        </is>
+      </c>
       <c r="Q266" s="2" t="n"/>
       <c r="R266" s="2" t="n"/>
       <c r="S266" s="2" t="n"/>
@@ -23099,10 +25047,18 @@
       <c r="L268" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M268" s="2" t="n"/>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N268" s="2" t="n"/>
       <c r="O268" s="2" t="n"/>
-      <c r="P268" s="2" t="n"/>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>Margi</t>
+        </is>
+      </c>
       <c r="Q268" s="2" t="n"/>
       <c r="R268" s="2" t="n"/>
       <c r="S268" s="2" t="n"/>
@@ -23183,10 +25139,18 @@
       <c r="L269" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M269" s="2" t="n"/>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N269" s="2" t="n"/>
       <c r="O269" s="2" t="n"/>
-      <c r="P269" s="2" t="n"/>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>Amargeti</t>
+        </is>
+      </c>
       <c r="Q269" s="2" t="n"/>
       <c r="R269" s="2" t="n"/>
       <c r="S269" s="2" t="n"/>
@@ -23267,10 +25231,18 @@
       <c r="L270" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M270" s="2" t="n"/>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N270" s="2" t="n"/>
       <c r="O270" s="2" t="n"/>
-      <c r="P270" s="2" t="n"/>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>Στενή</t>
+        </is>
+      </c>
       <c r="Q270" s="2" t="n"/>
       <c r="R270" s="2" t="n"/>
       <c r="S270" s="2" t="n"/>
@@ -23351,10 +25323,18 @@
       <c r="L271" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M271" s="2" t="n"/>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N271" s="2" t="n"/>
       <c r="O271" s="2" t="n"/>
-      <c r="P271" s="2" t="n"/>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>Theletra</t>
+        </is>
+      </c>
       <c r="Q271" s="2" t="n"/>
       <c r="R271" s="2" t="n"/>
       <c r="S271" s="2" t="n"/>
@@ -23435,10 +25415,18 @@
       <c r="L272" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M272" s="2" t="n"/>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N272" s="2" t="n"/>
       <c r="O272" s="2" t="n"/>
-      <c r="P272" s="2" t="n"/>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>Vouni</t>
+        </is>
+      </c>
       <c r="Q272" s="2" t="n"/>
       <c r="R272" s="2" t="n"/>
       <c r="S272" s="2" t="n"/>
@@ -23519,10 +25507,18 @@
       <c r="L273" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M273" s="2" t="n"/>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N273" s="2" t="n"/>
       <c r="O273" s="2" t="n"/>
-      <c r="P273" s="2" t="n"/>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>Linou</t>
+        </is>
+      </c>
       <c r="Q273" s="2" t="n"/>
       <c r="R273" s="2" t="n"/>
       <c r="S273" s="2" t="n"/>
@@ -23603,10 +25599,18 @@
       <c r="L274" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M274" s="2" t="n"/>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N274" s="2" t="n"/>
       <c r="O274" s="2" t="n"/>
-      <c r="P274" s="2" t="n"/>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>Δύμες</t>
+        </is>
+      </c>
       <c r="Q274" s="2" t="n"/>
       <c r="R274" s="2" t="n"/>
       <c r="S274" s="2" t="n"/>
@@ -23687,10 +25691,18 @@
       <c r="L275" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M275" s="2" t="n"/>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N275" s="2" t="n"/>
       <c r="O275" s="2" t="n"/>
-      <c r="P275" s="2" t="n"/>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>Nata</t>
+        </is>
+      </c>
       <c r="Q275" s="2" t="n"/>
       <c r="R275" s="2" t="n"/>
       <c r="S275" s="2" t="n"/>
@@ -23771,10 +25783,18 @@
       <c r="L276" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M276" s="2" t="n"/>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="2" t="n"/>
-      <c r="P276" s="2" t="n"/>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>Silikou</t>
+        </is>
+      </c>
       <c r="Q276" s="2" t="n"/>
       <c r="R276" s="2" t="n"/>
       <c r="S276" s="2" t="n"/>
@@ -23855,10 +25875,18 @@
       <c r="L277" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M277" s="2" t="n"/>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N277" s="2" t="n"/>
       <c r="O277" s="2" t="n"/>
-      <c r="P277" s="2" t="n"/>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>Ζωοπηγή</t>
+        </is>
+      </c>
       <c r="Q277" s="2" t="n"/>
       <c r="R277" s="2" t="n"/>
       <c r="S277" s="2" t="n"/>
@@ -23939,10 +25967,18 @@
       <c r="L278" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M278" s="2" t="n"/>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N278" s="2" t="n"/>
       <c r="O278" s="2" t="n"/>
-      <c r="P278" s="2" t="n"/>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>Pera Pedi</t>
+        </is>
+      </c>
       <c r="Q278" s="2" t="n"/>
       <c r="R278" s="2" t="n"/>
       <c r="S278" s="2" t="n"/>
@@ -24023,10 +26059,18 @@
       <c r="L279" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M279" s="2" t="n"/>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N279" s="2" t="n"/>
       <c r="O279" s="2" t="n"/>
-      <c r="P279" s="2" t="n"/>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>Kelokedara</t>
+        </is>
+      </c>
       <c r="Q279" s="2" t="n"/>
       <c r="R279" s="2" t="n"/>
       <c r="S279" s="2" t="n"/>
@@ -24107,10 +26151,18 @@
       <c r="L280" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M280" s="2" t="n"/>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N280" s="2" t="n"/>
       <c r="O280" s="2" t="n"/>
-      <c r="P280" s="2" t="n"/>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>Oikos</t>
+        </is>
+      </c>
       <c r="Q280" s="2" t="n"/>
       <c r="R280" s="2" t="n"/>
       <c r="S280" s="2" t="n"/>
@@ -24191,10 +26243,18 @@
       <c r="L281" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M281" s="2" t="n"/>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N281" s="2" t="n"/>
       <c r="O281" s="2" t="n"/>
-      <c r="P281" s="2" t="n"/>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>Pano Arodes</t>
+        </is>
+      </c>
       <c r="Q281" s="2" t="n"/>
       <c r="R281" s="2" t="n"/>
       <c r="S281" s="2" t="n"/>
@@ -24275,10 +26335,18 @@
       <c r="L282" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M282" s="2" t="n"/>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N282" s="2" t="n"/>
       <c r="O282" s="2" t="n"/>
-      <c r="P282" s="2" t="n"/>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>Pedoulas</t>
+        </is>
+      </c>
       <c r="Q282" s="2" t="n"/>
       <c r="R282" s="2" t="n"/>
       <c r="S282" s="2" t="n"/>
@@ -24359,10 +26427,18 @@
       <c r="L283" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M283" s="2" t="n"/>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N283" s="2" t="n"/>
       <c r="O283" s="2" t="n"/>
-      <c r="P283" s="2" t="n"/>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>Acheleia</t>
+        </is>
+      </c>
       <c r="Q283" s="2" t="n"/>
       <c r="R283" s="2" t="n"/>
       <c r="S283" s="2" t="n"/>
@@ -24443,10 +26519,18 @@
       <c r="L284" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M284" s="2" t="n"/>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N284" s="2" t="n"/>
       <c r="O284" s="2" t="n"/>
-      <c r="P284" s="2" t="n"/>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>Doros</t>
+        </is>
+      </c>
       <c r="Q284" s="2" t="n"/>
       <c r="R284" s="2" t="n"/>
       <c r="S284" s="2" t="n"/>
@@ -24527,10 +26611,18 @@
       <c r="L285" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M285" s="2" t="n"/>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N285" s="2" t="n"/>
       <c r="O285" s="2" t="n"/>
-      <c r="P285" s="2" t="n"/>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>Polystypos</t>
+        </is>
+      </c>
       <c r="Q285" s="2" t="n"/>
       <c r="R285" s="2" t="n"/>
       <c r="S285" s="2" t="n"/>
@@ -24611,10 +26703,18 @@
       <c r="L286" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M286" s="2" t="n"/>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N286" s="2" t="n"/>
       <c r="O286" s="2" t="n"/>
-      <c r="P286" s="2" t="n"/>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>Kannavia</t>
+        </is>
+      </c>
       <c r="Q286" s="2" t="n"/>
       <c r="R286" s="2" t="n"/>
       <c r="S286" s="2" t="n"/>
@@ -24815,10 +26915,18 @@
       <c r="L289" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M289" s="2" t="n"/>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N289" s="2" t="n"/>
       <c r="O289" s="2" t="n"/>
-      <c r="P289" s="2" t="n"/>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>Dora</t>
+        </is>
+      </c>
       <c r="Q289" s="2" t="n"/>
       <c r="R289" s="2" t="n"/>
       <c r="S289" s="2" t="n"/>
@@ -24899,10 +27007,18 @@
       <c r="L290" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M290" s="2" t="n"/>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N290" s="2" t="n"/>
       <c r="O290" s="2" t="n"/>
-      <c r="P290" s="2" t="n"/>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>Agios Georgios</t>
+        </is>
+      </c>
       <c r="Q290" s="2" t="n"/>
       <c r="R290" s="2" t="n"/>
       <c r="S290" s="2" t="n"/>
@@ -24983,10 +27099,18 @@
       <c r="L291" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M291" s="2" t="n"/>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N291" s="2" t="n"/>
       <c r="O291" s="2" t="n"/>
-      <c r="P291" s="2" t="n"/>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>Χανδριά</t>
+        </is>
+      </c>
       <c r="Q291" s="2" t="n"/>
       <c r="R291" s="2" t="n"/>
       <c r="S291" s="2" t="n"/>
@@ -25067,10 +27191,18 @@
       <c r="L292" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M292" s="2" t="n"/>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N292" s="2" t="n"/>
       <c r="O292" s="2" t="n"/>
-      <c r="P292" s="2" t="n"/>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>Moutoullas</t>
+        </is>
+      </c>
       <c r="Q292" s="2" t="n"/>
       <c r="R292" s="2" t="n"/>
       <c r="S292" s="2" t="n"/>
@@ -25151,10 +27283,18 @@
       <c r="L293" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M293" s="2" t="n"/>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N293" s="2" t="n"/>
       <c r="O293" s="2" t="n"/>
-      <c r="P293" s="2" t="n"/>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>Κάτω Πλάτρες</t>
+        </is>
+      </c>
       <c r="Q293" s="2" t="n"/>
       <c r="R293" s="2" t="n"/>
       <c r="S293" s="2" t="n"/>
@@ -25235,10 +27375,18 @@
       <c r="L294" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M294" s="2" t="n"/>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N294" s="2" t="n"/>
       <c r="O294" s="2" t="n"/>
-      <c r="P294" s="2" t="n"/>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>Choulou</t>
+        </is>
+      </c>
       <c r="Q294" s="2" t="n"/>
       <c r="R294" s="2" t="n"/>
       <c r="S294" s="2" t="n"/>
@@ -25319,10 +27467,18 @@
       <c r="L295" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M295" s="2" t="n"/>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="2" t="n"/>
-      <c r="P295" s="2" t="n"/>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>Άγιος Παύλος</t>
+        </is>
+      </c>
       <c r="Q295" s="2" t="n"/>
       <c r="R295" s="2" t="n"/>
       <c r="S295" s="2" t="n"/>
@@ -25403,10 +27559,18 @@
       <c r="L296" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M296" s="2" t="n"/>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N296" s="2" t="n"/>
       <c r="O296" s="2" t="n"/>
-      <c r="P296" s="2" t="n"/>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>Kato Lefkara</t>
+        </is>
+      </c>
       <c r="Q296" s="2" t="n"/>
       <c r="R296" s="2" t="n"/>
       <c r="S296" s="2" t="n"/>
@@ -25487,10 +27651,18 @@
       <c r="L297" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M297" s="2" t="n"/>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N297" s="2" t="n"/>
       <c r="O297" s="2" t="n"/>
-      <c r="P297" s="2" t="n"/>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>Xyliatos</t>
+        </is>
+      </c>
       <c r="Q297" s="2" t="n"/>
       <c r="R297" s="2" t="n"/>
       <c r="S297" s="2" t="n"/>
@@ -25571,10 +27743,18 @@
       <c r="L298" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M298" s="2" t="n"/>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N298" s="2" t="n"/>
       <c r="O298" s="2" t="n"/>
-      <c r="P298" s="2" t="n"/>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>Mandria</t>
+        </is>
+      </c>
       <c r="Q298" s="2" t="n"/>
       <c r="R298" s="2" t="n"/>
       <c r="S298" s="2" t="n"/>
@@ -25655,10 +27835,18 @@
       <c r="L299" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M299" s="2" t="n"/>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N299" s="2" t="n"/>
       <c r="O299" s="2" t="n"/>
-      <c r="P299" s="2" t="n"/>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>Χρυσοχού</t>
+        </is>
+      </c>
       <c r="Q299" s="2" t="n"/>
       <c r="R299" s="2" t="n"/>
       <c r="S299" s="2" t="n"/>
@@ -25739,10 +27927,18 @@
       <c r="L300" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M300" s="2" t="n"/>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N300" s="2" t="n"/>
       <c r="O300" s="2" t="n"/>
-      <c r="P300" s="2" t="n"/>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>Kato Drys</t>
+        </is>
+      </c>
       <c r="Q300" s="2" t="n"/>
       <c r="R300" s="2" t="n"/>
       <c r="S300" s="2" t="n"/>
@@ -25823,10 +28019,18 @@
       <c r="L301" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M301" s="2" t="n"/>
+      <c r="M301" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N301" s="2" t="n"/>
       <c r="O301" s="2" t="n"/>
-      <c r="P301" s="2" t="n"/>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>Άγιος Μάμας</t>
+        </is>
+      </c>
       <c r="Q301" s="2" t="n"/>
       <c r="R301" s="2" t="n"/>
       <c r="S301" s="2" t="n"/>
@@ -25907,10 +28111,18 @@
       <c r="L302" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M302" s="2" t="n"/>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N302" s="2" t="n"/>
       <c r="O302" s="2" t="n"/>
-      <c r="P302" s="2" t="n"/>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>Agioi Iliofotoi</t>
+        </is>
+      </c>
       <c r="Q302" s="2" t="n"/>
       <c r="R302" s="2" t="n"/>
       <c r="S302" s="2" t="n"/>
@@ -25991,10 +28203,18 @@
       <c r="L303" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M303" s="2" t="n"/>
+      <c r="M303" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N303" s="2" t="n"/>
       <c r="O303" s="2" t="n"/>
-      <c r="P303" s="2" t="n"/>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>Αγρίδια</t>
+        </is>
+      </c>
       <c r="Q303" s="2" t="n"/>
       <c r="R303" s="2" t="n"/>
       <c r="S303" s="2" t="n"/>
@@ -26075,10 +28295,18 @@
       <c r="L304" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M304" s="2" t="n"/>
+      <c r="M304" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N304" s="2" t="n"/>
       <c r="O304" s="2" t="n"/>
-      <c r="P304" s="2" t="n"/>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>Dörtyol</t>
+        </is>
+      </c>
       <c r="Q304" s="2" t="n"/>
       <c r="R304" s="2" t="n"/>
       <c r="S304" s="2" t="n"/>
@@ -26159,10 +28387,18 @@
       <c r="L305" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M305" s="2" t="n"/>
+      <c r="M305" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N305" s="2" t="n"/>
       <c r="O305" s="2" t="n"/>
-      <c r="P305" s="2" t="n"/>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>Spilia</t>
+        </is>
+      </c>
       <c r="Q305" s="2" t="n"/>
       <c r="R305" s="2" t="n"/>
       <c r="S305" s="2" t="n"/>
@@ -26243,10 +28479,18 @@
       <c r="L306" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M306" s="2" t="n"/>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N306" s="2" t="n"/>
       <c r="O306" s="2" t="n"/>
-      <c r="P306" s="2" t="n"/>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>Drymou</t>
+        </is>
+      </c>
       <c r="Q306" s="2" t="n"/>
       <c r="R306" s="2" t="n"/>
       <c r="S306" s="2" t="n"/>
@@ -26387,10 +28631,18 @@
       <c r="L308" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M308" s="2" t="n"/>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N308" s="2" t="n"/>
       <c r="O308" s="2" t="n"/>
-      <c r="P308" s="2" t="n"/>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>Mari</t>
+        </is>
+      </c>
       <c r="Q308" s="2" t="n"/>
       <c r="R308" s="2" t="n"/>
       <c r="S308" s="2" t="n"/>
@@ -26471,10 +28723,18 @@
       <c r="L309" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M309" s="2" t="n"/>
+      <c r="M309" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N309" s="2" t="n"/>
       <c r="O309" s="2" t="n"/>
-      <c r="P309" s="2" t="n"/>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>Psathi</t>
+        </is>
+      </c>
       <c r="Q309" s="2" t="n"/>
       <c r="R309" s="2" t="n"/>
       <c r="S309" s="2" t="n"/>
@@ -26555,10 +28815,18 @@
       <c r="L310" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M310" s="2" t="n"/>
+      <c r="M310" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N310" s="2" t="n"/>
       <c r="O310" s="2" t="n"/>
-      <c r="P310" s="2" t="n"/>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>Katydata</t>
+        </is>
+      </c>
       <c r="Q310" s="2" t="n"/>
       <c r="R310" s="2" t="n"/>
       <c r="S310" s="2" t="n"/>
@@ -26639,10 +28907,18 @@
       <c r="L311" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M311" s="2" t="n"/>
+      <c r="M311" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N311" s="2" t="n"/>
       <c r="O311" s="2" t="n"/>
-      <c r="P311" s="2" t="n"/>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>Agioi Vavatsinias</t>
+        </is>
+      </c>
       <c r="Q311" s="2" t="n"/>
       <c r="R311" s="2" t="n"/>
       <c r="S311" s="2" t="n"/>
@@ -26723,10 +28999,18 @@
       <c r="L312" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M312" s="2" t="n"/>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N312" s="2" t="n"/>
       <c r="O312" s="2" t="n"/>
-      <c r="P312" s="2" t="n"/>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>Askas</t>
+        </is>
+      </c>
       <c r="Q312" s="2" t="n"/>
       <c r="R312" s="2" t="n"/>
       <c r="S312" s="2" t="n"/>
@@ -26807,10 +29091,18 @@
       <c r="L313" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M313" s="2" t="n"/>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N313" s="2" t="n"/>
       <c r="O313" s="2" t="n"/>
-      <c r="P313" s="2" t="n"/>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>Melini</t>
+        </is>
+      </c>
       <c r="Q313" s="2" t="n"/>
       <c r="R313" s="2" t="n"/>
       <c r="S313" s="2" t="n"/>
@@ -26891,10 +29183,18 @@
       <c r="L314" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M314" s="2" t="n"/>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N314" s="2" t="n"/>
       <c r="O314" s="2" t="n"/>
-      <c r="P314" s="2" t="n"/>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>Gerasa</t>
+        </is>
+      </c>
       <c r="Q314" s="2" t="n"/>
       <c r="R314" s="2" t="n"/>
       <c r="S314" s="2" t="n"/>
@@ -26975,10 +29275,18 @@
       <c r="L315" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M315" s="2" t="n"/>
+      <c r="M315" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N315" s="2" t="n"/>
       <c r="O315" s="2" t="n"/>
-      <c r="P315" s="2" t="n"/>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>Agios Georgios</t>
+        </is>
+      </c>
       <c r="Q315" s="2" t="n"/>
       <c r="R315" s="2" t="n"/>
       <c r="S315" s="2" t="n"/>
@@ -27059,10 +29367,18 @@
       <c r="L316" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M316" s="2" t="n"/>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N316" s="2" t="n"/>
       <c r="O316" s="2" t="n"/>
-      <c r="P316" s="2" t="n"/>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>Kampi</t>
+        </is>
+      </c>
       <c r="Q316" s="2" t="n"/>
       <c r="R316" s="2" t="n"/>
       <c r="S316" s="2" t="n"/>
@@ -27143,10 +29459,18 @@
       <c r="L317" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M317" s="2" t="n"/>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N317" s="2" t="n"/>
       <c r="O317" s="2" t="n"/>
-      <c r="P317" s="2" t="n"/>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>Tsakistra</t>
+        </is>
+      </c>
       <c r="Q317" s="2" t="n"/>
       <c r="R317" s="2" t="n"/>
       <c r="S317" s="2" t="n"/>
@@ -27227,10 +29551,18 @@
       <c r="L318" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M318" s="2" t="n"/>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N318" s="2" t="n"/>
       <c r="O318" s="2" t="n"/>
-      <c r="P318" s="2" t="n"/>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>Lofou</t>
+        </is>
+      </c>
       <c r="Q318" s="2" t="n"/>
       <c r="R318" s="2" t="n"/>
       <c r="S318" s="2" t="n"/>
@@ -27311,10 +29643,18 @@
       <c r="L319" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M319" s="2" t="n"/>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N319" s="2" t="n"/>
       <c r="O319" s="2" t="n"/>
-      <c r="P319" s="2" t="n"/>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>Πηγένια</t>
+        </is>
+      </c>
       <c r="Q319" s="2" t="n"/>
       <c r="R319" s="2" t="n"/>
       <c r="S319" s="2" t="n"/>
@@ -27455,10 +29795,18 @@
       <c r="L321" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M321" s="2" t="n"/>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N321" s="2" t="n"/>
       <c r="O321" s="2" t="n"/>
-      <c r="P321" s="2" t="n"/>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>Fyti</t>
+        </is>
+      </c>
       <c r="Q321" s="2" t="n"/>
       <c r="R321" s="2" t="n"/>
       <c r="S321" s="2" t="n"/>
@@ -27539,10 +29887,18 @@
       <c r="L322" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M322" s="2" t="n"/>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N322" s="2" t="n"/>
       <c r="O322" s="2" t="n"/>
-      <c r="P322" s="2" t="n"/>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Προδρόμου</t>
+        </is>
+      </c>
       <c r="Q322" s="2" t="n"/>
       <c r="R322" s="2" t="n"/>
       <c r="S322" s="2" t="n"/>
@@ -27623,10 +29979,18 @@
       <c r="L323" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M323" s="2" t="n"/>
+      <c r="M323" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N323" s="2" t="n"/>
       <c r="O323" s="2" t="n"/>
-      <c r="P323" s="2" t="n"/>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>Vavatsinia</t>
+        </is>
+      </c>
       <c r="Q323" s="2" t="n"/>
       <c r="R323" s="2" t="n"/>
       <c r="S323" s="2" t="n"/>
@@ -27707,10 +30071,18 @@
       <c r="L324" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M324" s="2" t="n"/>
+      <c r="M324" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N324" s="2" t="n"/>
       <c r="O324" s="2" t="n"/>
-      <c r="P324" s="2" t="n"/>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>Χόλη</t>
+        </is>
+      </c>
       <c r="Q324" s="2" t="n"/>
       <c r="R324" s="2" t="n"/>
       <c r="S324" s="2" t="n"/>
@@ -27791,10 +30163,18 @@
       <c r="L325" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M325" s="2" t="n"/>
+      <c r="M325" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N325" s="2" t="n"/>
       <c r="O325" s="2" t="n"/>
-      <c r="P325" s="2" t="n"/>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>Σοφτάδες</t>
+        </is>
+      </c>
       <c r="Q325" s="2" t="n"/>
       <c r="R325" s="2" t="n"/>
       <c r="S325" s="2" t="n"/>
@@ -27875,10 +30255,18 @@
       <c r="L326" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M326" s="2" t="n"/>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N326" s="2" t="n"/>
       <c r="O326" s="2" t="n"/>
-      <c r="P326" s="2" t="n"/>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>Σκούλλι</t>
+        </is>
+      </c>
       <c r="Q326" s="2" t="n"/>
       <c r="R326" s="2" t="n"/>
       <c r="S326" s="2" t="n"/>
@@ -28019,10 +30407,18 @@
       <c r="L328" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M328" s="2" t="n"/>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N328" s="2" t="n"/>
       <c r="O328" s="2" t="n"/>
-      <c r="P328" s="2" t="n"/>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Λεμύθου</t>
+        </is>
+      </c>
       <c r="Q328" s="2" t="n"/>
       <c r="R328" s="2" t="n"/>
       <c r="S328" s="2" t="n"/>
@@ -28103,10 +30499,18 @@
       <c r="L329" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M329" s="2" t="n"/>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N329" s="2" t="n"/>
       <c r="O329" s="2" t="n"/>
-      <c r="P329" s="2" t="n"/>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>Agios Dimitrianos</t>
+        </is>
+      </c>
       <c r="Q329" s="2" t="n"/>
       <c r="R329" s="2" t="n"/>
       <c r="S329" s="2" t="n"/>
@@ -28187,10 +30591,18 @@
       <c r="L330" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M330" s="2" t="n"/>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N330" s="2" t="n"/>
       <c r="O330" s="2" t="n"/>
-      <c r="P330" s="2" t="n"/>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>Μακούντα</t>
+        </is>
+      </c>
       <c r="Q330" s="2" t="n"/>
       <c r="R330" s="2" t="n"/>
       <c r="S330" s="2" t="n"/>
@@ -28271,10 +30683,18 @@
       <c r="L331" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M331" s="2" t="n"/>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N331" s="2" t="n"/>
       <c r="O331" s="2" t="n"/>
-      <c r="P331" s="2" t="n"/>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>Platanistasa</t>
+        </is>
+      </c>
       <c r="Q331" s="2" t="n"/>
       <c r="R331" s="2" t="n"/>
       <c r="S331" s="2" t="n"/>
@@ -28355,10 +30775,18 @@
       <c r="L332" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M332" s="2" t="n"/>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N332" s="2" t="n"/>
       <c r="O332" s="2" t="n"/>
-      <c r="P332" s="2" t="n"/>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>Kritou Marottou</t>
+        </is>
+      </c>
       <c r="Q332" s="2" t="n"/>
       <c r="R332" s="2" t="n"/>
       <c r="S332" s="2" t="n"/>
@@ -28439,10 +30867,18 @@
       <c r="L333" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M333" s="2" t="n"/>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N333" s="2" t="n"/>
       <c r="O333" s="2" t="n"/>
-      <c r="P333" s="2" t="n"/>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>Kritou Tera</t>
+        </is>
+      </c>
       <c r="Q333" s="2" t="n"/>
       <c r="R333" s="2" t="n"/>
       <c r="S333" s="2" t="n"/>
@@ -28523,10 +30959,18 @@
       <c r="L334" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M334" s="2" t="n"/>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N334" s="2" t="n"/>
       <c r="O334" s="2" t="n"/>
-      <c r="P334" s="2" t="n"/>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>Fterikoudi</t>
+        </is>
+      </c>
       <c r="Q334" s="2" t="n"/>
       <c r="R334" s="2" t="n"/>
       <c r="S334" s="2" t="n"/>
@@ -28667,10 +31111,18 @@
       <c r="L336" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M336" s="2" t="n"/>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N336" s="2" t="n"/>
       <c r="O336" s="2" t="n"/>
-      <c r="P336" s="2" t="n"/>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>Malia</t>
+        </is>
+      </c>
       <c r="Q336" s="2" t="n"/>
       <c r="R336" s="2" t="n"/>
       <c r="S336" s="2" t="n"/>
@@ -28751,10 +31203,18 @@
       <c r="L337" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M337" s="2" t="n"/>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N337" s="2" t="n"/>
       <c r="O337" s="2" t="n"/>
-      <c r="P337" s="2" t="n"/>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>Ποταμίτισσα</t>
+        </is>
+      </c>
       <c r="Q337" s="2" t="n"/>
       <c r="R337" s="2" t="n"/>
       <c r="S337" s="2" t="n"/>
@@ -28835,10 +31295,18 @@
       <c r="L338" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M338" s="2" t="n"/>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N338" s="2" t="n"/>
       <c r="O338" s="2" t="n"/>
-      <c r="P338" s="2" t="n"/>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>Axylou</t>
+        </is>
+      </c>
       <c r="Q338" s="2" t="n"/>
       <c r="R338" s="2" t="n"/>
       <c r="S338" s="2" t="n"/>
@@ -28919,10 +31387,18 @@
       <c r="L339" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M339" s="2" t="n"/>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N339" s="2" t="n"/>
       <c r="O339" s="2" t="n"/>
-      <c r="P339" s="2" t="n"/>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>Kato Koutrafas</t>
+        </is>
+      </c>
       <c r="Q339" s="2" t="n"/>
       <c r="R339" s="2" t="n"/>
       <c r="S339" s="2" t="n"/>
@@ -29003,10 +31479,18 @@
       <c r="L340" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M340" s="2" t="n"/>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N340" s="2" t="n"/>
       <c r="O340" s="2" t="n"/>
-      <c r="P340" s="2" t="n"/>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>Σανίδα</t>
+        </is>
+      </c>
       <c r="Q340" s="2" t="n"/>
       <c r="R340" s="2" t="n"/>
       <c r="S340" s="2" t="n"/>
@@ -29087,10 +31571,18 @@
       <c r="L341" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M341" s="2" t="n"/>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N341" s="2" t="n"/>
       <c r="O341" s="2" t="n"/>
-      <c r="P341" s="2" t="n"/>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>Αγιος Θεόδωρος</t>
+        </is>
+      </c>
       <c r="Q341" s="2" t="n"/>
       <c r="R341" s="2" t="n"/>
       <c r="S341" s="2" t="n"/>
@@ -29171,10 +31663,18 @@
       <c r="L342" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M342" s="2" t="n"/>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N342" s="2" t="n"/>
       <c r="O342" s="2" t="n"/>
-      <c r="P342" s="2" t="n"/>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>Kapileio</t>
+        </is>
+      </c>
       <c r="Q342" s="2" t="n"/>
       <c r="R342" s="2" t="n"/>
       <c r="S342" s="2" t="n"/>
@@ -29255,10 +31755,18 @@
       <c r="L343" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M343" s="2" t="n"/>
+      <c r="M343" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N343" s="2" t="n"/>
       <c r="O343" s="2" t="n"/>
-      <c r="P343" s="2" t="n"/>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>Pentalia</t>
+        </is>
+      </c>
       <c r="Q343" s="2" t="n"/>
       <c r="R343" s="2" t="n"/>
       <c r="S343" s="2" t="n"/>
@@ -29339,10 +31847,18 @@
       <c r="L344" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M344" s="2" t="n"/>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N344" s="2" t="n"/>
       <c r="O344" s="2" t="n"/>
-      <c r="P344" s="2" t="n"/>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>Yamaçköy</t>
+        </is>
+      </c>
       <c r="Q344" s="2" t="n"/>
       <c r="R344" s="2" t="n"/>
       <c r="S344" s="2" t="n"/>
@@ -29423,10 +31939,18 @@
       <c r="L345" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M345" s="2" t="n"/>
+      <c r="M345" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N345" s="2" t="n"/>
       <c r="O345" s="2" t="n"/>
-      <c r="P345" s="2" t="n"/>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>Lagoudera</t>
+        </is>
+      </c>
       <c r="Q345" s="2" t="n"/>
       <c r="R345" s="2" t="n"/>
       <c r="S345" s="2" t="n"/>
@@ -29507,10 +32031,18 @@
       <c r="L346" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M346" s="2" t="n"/>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N346" s="2" t="n"/>
       <c r="O346" s="2" t="n"/>
-      <c r="P346" s="2" t="n"/>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>Παχύαμμος</t>
+        </is>
+      </c>
       <c r="Q346" s="2" t="n"/>
       <c r="R346" s="2" t="n"/>
       <c r="S346" s="2" t="n"/>
@@ -29591,10 +32123,18 @@
       <c r="L347" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M347" s="2" t="n"/>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N347" s="2" t="n"/>
       <c r="O347" s="2" t="n"/>
-      <c r="P347" s="2" t="n"/>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>Αγιος Θεόδωρος</t>
+        </is>
+      </c>
       <c r="Q347" s="2" t="n"/>
       <c r="R347" s="2" t="n"/>
       <c r="S347" s="2" t="n"/>
@@ -29675,10 +32215,18 @@
       <c r="L348" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M348" s="2" t="n"/>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N348" s="2" t="n"/>
       <c r="O348" s="2" t="n"/>
-      <c r="P348" s="2" t="n"/>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>Miliou</t>
+        </is>
+      </c>
       <c r="Q348" s="2" t="n"/>
       <c r="R348" s="2" t="n"/>
       <c r="S348" s="2" t="n"/>
@@ -29759,10 +32307,18 @@
       <c r="L349" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M349" s="2" t="n"/>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N349" s="2" t="n"/>
       <c r="O349" s="2" t="n"/>
-      <c r="P349" s="2" t="n"/>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>Κάτω Μύλος</t>
+        </is>
+      </c>
       <c r="Q349" s="2" t="n"/>
       <c r="R349" s="2" t="n"/>
       <c r="S349" s="2" t="n"/>
@@ -29843,10 +32399,18 @@
       <c r="L350" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M350" s="2" t="n"/>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N350" s="2" t="n"/>
       <c r="O350" s="2" t="n"/>
-      <c r="P350" s="2" t="n"/>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>Lasa</t>
+        </is>
+      </c>
       <c r="Q350" s="2" t="n"/>
       <c r="R350" s="2" t="n"/>
       <c r="S350" s="2" t="n"/>
@@ -29927,10 +32491,18 @@
       <c r="L351" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M351" s="2" t="n"/>
+      <c r="M351" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N351" s="2" t="n"/>
       <c r="O351" s="2" t="n"/>
-      <c r="P351" s="2" t="n"/>
+      <c r="P351" s="2" t="inlineStr">
+        <is>
+          <t>Asprogia</t>
+        </is>
+      </c>
       <c r="Q351" s="2" t="n"/>
       <c r="R351" s="2" t="n"/>
       <c r="S351" s="2" t="n"/>
@@ -30011,10 +32583,18 @@
       <c r="L352" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M352" s="2" t="n"/>
+      <c r="M352" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N352" s="2" t="n"/>
       <c r="O352" s="2" t="n"/>
-      <c r="P352" s="2" t="n"/>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>Alektora</t>
+        </is>
+      </c>
       <c r="Q352" s="2" t="n"/>
       <c r="R352" s="2" t="n"/>
       <c r="S352" s="2" t="n"/>
@@ -30095,10 +32675,18 @@
       <c r="L353" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M353" s="2" t="n"/>
+      <c r="M353" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N353" s="2" t="n"/>
       <c r="O353" s="2" t="n"/>
-      <c r="P353" s="2" t="n"/>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>Νέα Δήμματα</t>
+        </is>
+      </c>
       <c r="Q353" s="2" t="n"/>
       <c r="R353" s="2" t="n"/>
       <c r="S353" s="2" t="n"/>
@@ -30179,10 +32767,18 @@
       <c r="L354" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M354" s="2" t="n"/>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N354" s="2" t="n"/>
       <c r="O354" s="2" t="n"/>
-      <c r="P354" s="2" t="n"/>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>Πελαθούσα</t>
+        </is>
+      </c>
       <c r="Q354" s="2" t="n"/>
       <c r="R354" s="2" t="n"/>
       <c r="S354" s="2" t="n"/>
@@ -30263,10 +32859,18 @@
       <c r="L355" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M355" s="2" t="n"/>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N355" s="2" t="n"/>
       <c r="O355" s="2" t="n"/>
-      <c r="P355" s="2" t="n"/>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>Κάτω Ακουρδάλια</t>
+        </is>
+      </c>
       <c r="Q355" s="2" t="n"/>
       <c r="R355" s="2" t="n"/>
       <c r="S355" s="2" t="n"/>
@@ -30347,10 +32951,18 @@
       <c r="L356" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M356" s="2" t="n"/>
+      <c r="M356" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N356" s="2" t="n"/>
       <c r="O356" s="2" t="n"/>
-      <c r="P356" s="2" t="n"/>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>Τσερκέζοι</t>
+        </is>
+      </c>
       <c r="Q356" s="2" t="n"/>
       <c r="R356" s="2" t="n"/>
       <c r="S356" s="2" t="n"/>
@@ -30431,10 +33043,18 @@
       <c r="L357" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M357" s="2" t="n"/>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N357" s="2" t="n"/>
       <c r="O357" s="2" t="n"/>
-      <c r="P357" s="2" t="n"/>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>Stavrokonnou</t>
+        </is>
+      </c>
       <c r="Q357" s="2" t="n"/>
       <c r="R357" s="2" t="n"/>
       <c r="S357" s="2" t="n"/>
@@ -30515,10 +33135,18 @@
       <c r="L358" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M358" s="2" t="n"/>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N358" s="2" t="n"/>
       <c r="O358" s="2" t="n"/>
-      <c r="P358" s="2" t="n"/>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>Gerakies</t>
+        </is>
+      </c>
       <c r="Q358" s="2" t="n"/>
       <c r="R358" s="2" t="n"/>
       <c r="S358" s="2" t="n"/>
@@ -30599,10 +33227,18 @@
       <c r="L359" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M359" s="2" t="n"/>
+      <c r="M359" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N359" s="2" t="n"/>
       <c r="O359" s="2" t="n"/>
-      <c r="P359" s="2" t="n"/>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>Vavla</t>
+        </is>
+      </c>
       <c r="Q359" s="2" t="n"/>
       <c r="R359" s="2" t="n"/>
       <c r="S359" s="2" t="n"/>
@@ -30683,10 +33319,18 @@
       <c r="L360" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M360" s="2" t="n"/>
+      <c r="M360" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N360" s="2" t="n"/>
       <c r="O360" s="2" t="n"/>
-      <c r="P360" s="2" t="n"/>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>Mamonia</t>
+        </is>
+      </c>
       <c r="Q360" s="2" t="n"/>
       <c r="R360" s="2" t="n"/>
       <c r="S360" s="2" t="n"/>
@@ -30767,10 +33411,18 @@
       <c r="L361" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M361" s="2" t="n"/>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N361" s="2" t="n"/>
       <c r="O361" s="2" t="n"/>
-      <c r="P361" s="2" t="n"/>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>Kato Arodes</t>
+        </is>
+      </c>
       <c r="Q361" s="2" t="n"/>
       <c r="R361" s="2" t="n"/>
       <c r="S361" s="2" t="n"/>
@@ -30851,10 +33503,18 @@
       <c r="L362" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M362" s="2" t="n"/>
+      <c r="M362" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N362" s="2" t="n"/>
       <c r="O362" s="2" t="n"/>
-      <c r="P362" s="2" t="n"/>
+      <c r="P362" s="2" t="inlineStr">
+        <is>
+          <t>Lazanias</t>
+        </is>
+      </c>
       <c r="Q362" s="2" t="n"/>
       <c r="R362" s="2" t="n"/>
       <c r="S362" s="2" t="n"/>
@@ -30935,10 +33595,18 @@
       <c r="L363" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M363" s="2" t="n"/>
+      <c r="M363" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N363" s="2" t="n"/>
       <c r="O363" s="2" t="n"/>
-      <c r="P363" s="2" t="n"/>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>Galataria</t>
+        </is>
+      </c>
       <c r="Q363" s="2" t="n"/>
       <c r="R363" s="2" t="n"/>
       <c r="S363" s="2" t="n"/>
@@ -31019,10 +33687,18 @@
       <c r="L364" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M364" s="2" t="n"/>
+      <c r="M364" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N364" s="2" t="n"/>
       <c r="O364" s="2" t="n"/>
-      <c r="P364" s="2" t="n"/>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>Thrinia</t>
+        </is>
+      </c>
       <c r="Q364" s="2" t="n"/>
       <c r="R364" s="2" t="n"/>
       <c r="S364" s="2" t="n"/>
@@ -31163,10 +33839,18 @@
       <c r="L366" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M366" s="2" t="n"/>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N366" s="2" t="n"/>
       <c r="O366" s="2" t="n"/>
-      <c r="P366" s="2" t="n"/>
+      <c r="P366" s="2" t="inlineStr">
+        <is>
+          <t>Trachypedoula</t>
+        </is>
+      </c>
       <c r="Q366" s="2" t="n"/>
       <c r="R366" s="2" t="n"/>
       <c r="S366" s="2" t="n"/>
@@ -31247,10 +33931,18 @@
       <c r="L367" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M367" s="2" t="n"/>
+      <c r="M367" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N367" s="2" t="n"/>
       <c r="O367" s="2" t="n"/>
-      <c r="P367" s="2" t="n"/>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>Lemona</t>
+        </is>
+      </c>
       <c r="Q367" s="2" t="n"/>
       <c r="R367" s="2" t="n"/>
       <c r="S367" s="2" t="n"/>
@@ -31331,10 +34023,18 @@
       <c r="L368" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M368" s="2" t="n"/>
+      <c r="M368" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N368" s="2" t="n"/>
       <c r="O368" s="2" t="n"/>
-      <c r="P368" s="2" t="n"/>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>Agios Thomas</t>
+        </is>
+      </c>
       <c r="Q368" s="2" t="n"/>
       <c r="R368" s="2" t="n"/>
       <c r="S368" s="2" t="n"/>
@@ -31415,10 +34115,18 @@
       <c r="L369" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M369" s="2" t="n"/>
+      <c r="M369" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N369" s="2" t="n"/>
       <c r="O369" s="2" t="n"/>
-      <c r="P369" s="2" t="n"/>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>Ακαπνού</t>
+        </is>
+      </c>
       <c r="Q369" s="2" t="n"/>
       <c r="R369" s="2" t="n"/>
       <c r="S369" s="2" t="n"/>
@@ -31499,10 +34207,18 @@
       <c r="L370" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M370" s="2" t="n"/>
+      <c r="M370" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N370" s="2" t="n"/>
       <c r="O370" s="2" t="n"/>
-      <c r="P370" s="2" t="n"/>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>Menogeia</t>
+        </is>
+      </c>
       <c r="Q370" s="2" t="n"/>
       <c r="R370" s="2" t="n"/>
       <c r="S370" s="2" t="n"/>
@@ -31583,10 +34299,18 @@
       <c r="L371" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M371" s="2" t="n"/>
+      <c r="M371" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N371" s="2" t="n"/>
       <c r="O371" s="2" t="n"/>
-      <c r="P371" s="2" t="n"/>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Αγίου Δημητρίου</t>
+        </is>
+      </c>
       <c r="Q371" s="2" t="n"/>
       <c r="R371" s="2" t="n"/>
       <c r="S371" s="2" t="n"/>
@@ -31667,10 +34391,18 @@
       <c r="L372" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M372" s="2" t="n"/>
+      <c r="M372" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N372" s="2" t="n"/>
       <c r="O372" s="2" t="n"/>
-      <c r="P372" s="2" t="n"/>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>Alona</t>
+        </is>
+      </c>
       <c r="Q372" s="2" t="n"/>
       <c r="R372" s="2" t="n"/>
       <c r="S372" s="2" t="n"/>
@@ -31751,10 +34483,18 @@
       <c r="L373" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M373" s="2" t="n"/>
+      <c r="M373" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N373" s="2" t="n"/>
       <c r="O373" s="2" t="n"/>
-      <c r="P373" s="2" t="n"/>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>Kedares</t>
+        </is>
+      </c>
       <c r="Q373" s="2" t="n"/>
       <c r="R373" s="2" t="n"/>
       <c r="S373" s="2" t="n"/>
@@ -31835,10 +34575,18 @@
       <c r="L374" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M374" s="2" t="n"/>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N374" s="2" t="n"/>
       <c r="O374" s="2" t="n"/>
-      <c r="P374" s="2" t="n"/>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>Agios Ioannis</t>
+        </is>
+      </c>
       <c r="Q374" s="2" t="n"/>
       <c r="R374" s="2" t="n"/>
       <c r="S374" s="2" t="n"/>
@@ -31919,10 +34667,18 @@
       <c r="L375" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M375" s="2" t="n"/>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N375" s="2" t="n"/>
       <c r="O375" s="2" t="n"/>
-      <c r="P375" s="2" t="n"/>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>Potamiou</t>
+        </is>
+      </c>
       <c r="Q375" s="2" t="n"/>
       <c r="R375" s="2" t="n"/>
       <c r="S375" s="2" t="n"/>
@@ -32063,10 +34819,18 @@
       <c r="L377" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M377" s="2" t="n"/>
+      <c r="M377" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N377" s="2" t="n"/>
       <c r="O377" s="2" t="n"/>
-      <c r="P377" s="2" t="n"/>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>Akoursos</t>
+        </is>
+      </c>
       <c r="Q377" s="2" t="n"/>
       <c r="R377" s="2" t="n"/>
       <c r="S377" s="2" t="n"/>
@@ -32147,10 +34911,18 @@
       <c r="L378" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M378" s="2" t="n"/>
+      <c r="M378" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N378" s="2" t="n"/>
       <c r="O378" s="2" t="n"/>
-      <c r="P378" s="2" t="n"/>
+      <c r="P378" s="2" t="inlineStr">
+        <is>
+          <t>Delikipos</t>
+        </is>
+      </c>
       <c r="Q378" s="2" t="n"/>
       <c r="R378" s="2" t="n"/>
       <c r="S378" s="2" t="n"/>
@@ -32231,10 +35003,18 @@
       <c r="L379" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M379" s="2" t="n"/>
+      <c r="M379" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N379" s="2" t="n"/>
       <c r="O379" s="2" t="n"/>
-      <c r="P379" s="2" t="n"/>
+      <c r="P379" s="2" t="inlineStr">
+        <is>
+          <t>Lageia</t>
+        </is>
+      </c>
       <c r="Q379" s="2" t="n"/>
       <c r="R379" s="2" t="n"/>
       <c r="S379" s="2" t="n"/>
@@ -32315,10 +35095,18 @@
       <c r="L380" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M380" s="2" t="n"/>
+      <c r="M380" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N380" s="2" t="n"/>
       <c r="O380" s="2" t="n"/>
-      <c r="P380" s="2" t="n"/>
+      <c r="P380" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Τρεις Ελιές</t>
+        </is>
+      </c>
       <c r="Q380" s="2" t="n"/>
       <c r="R380" s="2" t="n"/>
       <c r="S380" s="2" t="n"/>
@@ -32399,10 +35187,18 @@
       <c r="L381" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M381" s="2" t="n"/>
+      <c r="M381" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N381" s="2" t="n"/>
       <c r="O381" s="2" t="n"/>
-      <c r="P381" s="2" t="n"/>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>Eledio</t>
+        </is>
+      </c>
       <c r="Q381" s="2" t="n"/>
       <c r="R381" s="2" t="n"/>
       <c r="S381" s="2" t="n"/>
@@ -32483,10 +35279,18 @@
       <c r="L382" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M382" s="2" t="n"/>
+      <c r="M382" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N382" s="2" t="n"/>
       <c r="O382" s="2" t="n"/>
-      <c r="P382" s="2" t="n"/>
+      <c r="P382" s="2" t="inlineStr">
+        <is>
+          <t>Pano Akourdaleia</t>
+        </is>
+      </c>
       <c r="Q382" s="2" t="n"/>
       <c r="R382" s="2" t="n"/>
       <c r="S382" s="2" t="n"/>
@@ -32567,10 +35371,18 @@
       <c r="L383" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M383" s="2" t="n"/>
+      <c r="M383" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N383" s="2" t="n"/>
       <c r="O383" s="2" t="n"/>
-      <c r="P383" s="2" t="n"/>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>Platanisteia</t>
+        </is>
+      </c>
       <c r="Q383" s="2" t="n"/>
       <c r="R383" s="2" t="n"/>
       <c r="S383" s="2" t="n"/>
@@ -32651,10 +35463,18 @@
       <c r="L384" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M384" s="2" t="n"/>
+      <c r="M384" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N384" s="2" t="n"/>
       <c r="O384" s="2" t="n"/>
-      <c r="P384" s="2" t="n"/>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>Arminou</t>
+        </is>
+      </c>
       <c r="Q384" s="2" t="n"/>
       <c r="R384" s="2" t="n"/>
       <c r="S384" s="2" t="n"/>
@@ -32735,10 +35555,18 @@
       <c r="L385" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M385" s="2" t="n"/>
+      <c r="M385" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N385" s="2" t="n"/>
       <c r="O385" s="2" t="n"/>
-      <c r="P385" s="2" t="n"/>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>Akdeniz</t>
+        </is>
+      </c>
       <c r="Q385" s="2" t="n"/>
       <c r="R385" s="2" t="n"/>
       <c r="S385" s="2" t="n"/>
@@ -32879,10 +35707,18 @@
       <c r="L387" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M387" s="2" t="n"/>
+      <c r="M387" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N387" s="2" t="n"/>
       <c r="O387" s="2" t="n"/>
-      <c r="P387" s="2" t="n"/>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>Ανδρολύκου</t>
+        </is>
+      </c>
       <c r="Q387" s="2" t="n"/>
       <c r="R387" s="2" t="n"/>
       <c r="S387" s="2" t="n"/>
@@ -33023,10 +35859,18 @@
       <c r="L389" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M389" s="2" t="n"/>
+      <c r="M389" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N389" s="2" t="n"/>
       <c r="O389" s="2" t="n"/>
-      <c r="P389" s="2" t="n"/>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>Praitori</t>
+        </is>
+      </c>
       <c r="Q389" s="2" t="n"/>
       <c r="R389" s="2" t="n"/>
       <c r="S389" s="2" t="n"/>
@@ -33107,10 +35951,18 @@
       <c r="L390" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M390" s="2" t="n"/>
+      <c r="M390" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N390" s="2" t="n"/>
       <c r="O390" s="2" t="n"/>
-      <c r="P390" s="2" t="n"/>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>Pano Archimandrita</t>
+        </is>
+      </c>
       <c r="Q390" s="2" t="n"/>
       <c r="R390" s="2" t="n"/>
       <c r="S390" s="2" t="n"/>
@@ -33191,10 +36043,18 @@
       <c r="L391" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M391" s="2" t="n"/>
+      <c r="M391" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N391" s="2" t="n"/>
       <c r="O391" s="2" t="n"/>
-      <c r="P391" s="2" t="n"/>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>Fikardou</t>
+        </is>
+      </c>
       <c r="Q391" s="2" t="n"/>
       <c r="R391" s="2" t="n"/>
       <c r="S391" s="2" t="n"/>
@@ -33275,10 +36135,18 @@
       <c r="L392" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M392" s="2" t="n"/>
+      <c r="M392" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N392" s="2" t="n"/>
       <c r="O392" s="2" t="n"/>
-      <c r="P392" s="2" t="n"/>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>Koilineia</t>
+        </is>
+      </c>
       <c r="Q392" s="2" t="n"/>
       <c r="R392" s="2" t="n"/>
       <c r="S392" s="2" t="n"/>
@@ -33359,10 +36227,18 @@
       <c r="L393" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M393" s="2" t="n"/>
+      <c r="M393" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N393" s="2" t="n"/>
       <c r="O393" s="2" t="n"/>
-      <c r="P393" s="2" t="n"/>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>Mesana</t>
+        </is>
+      </c>
       <c r="Q393" s="2" t="n"/>
       <c r="R393" s="2" t="n"/>
       <c r="S393" s="2" t="n"/>
@@ -33443,10 +36319,18 @@
       <c r="L394" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M394" s="2" t="n"/>
+      <c r="M394" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N394" s="2" t="n"/>
       <c r="O394" s="2" t="n"/>
-      <c r="P394" s="2" t="n"/>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>Saranti</t>
+        </is>
+      </c>
       <c r="Q394" s="2" t="n"/>
       <c r="R394" s="2" t="n"/>
       <c r="S394" s="2" t="n"/>
@@ -33527,10 +36411,18 @@
       <c r="L395" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M395" s="2" t="n"/>
+      <c r="M395" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N395" s="2" t="n"/>
       <c r="O395" s="2" t="n"/>
-      <c r="P395" s="2" t="n"/>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>Κλωνάρι</t>
+        </is>
+      </c>
       <c r="Q395" s="2" t="n"/>
       <c r="R395" s="2" t="n"/>
       <c r="S395" s="2" t="n"/>
@@ -33611,10 +36503,18 @@
       <c r="L396" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M396" s="2" t="n"/>
+      <c r="M396" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N396" s="2" t="n"/>
       <c r="O396" s="2" t="n"/>
-      <c r="P396" s="2" t="n"/>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>Mosfili</t>
+        </is>
+      </c>
       <c r="Q396" s="2" t="n"/>
       <c r="R396" s="2" t="n"/>
       <c r="S396" s="2" t="n"/>
@@ -33695,10 +36595,18 @@
       <c r="L397" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M397" s="2" t="n"/>
+      <c r="M397" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N397" s="2" t="n"/>
       <c r="O397" s="2" t="n"/>
-      <c r="P397" s="2" t="n"/>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Καμιναρίων</t>
+        </is>
+      </c>
       <c r="Q397" s="2" t="n"/>
       <c r="R397" s="2" t="n"/>
       <c r="S397" s="2" t="n"/>
@@ -33779,10 +36687,18 @@
       <c r="L398" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M398" s="2" t="n"/>
+      <c r="M398" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N398" s="2" t="n"/>
       <c r="O398" s="2" t="n"/>
-      <c r="P398" s="2" t="n"/>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>Meladeia</t>
+        </is>
+      </c>
       <c r="Q398" s="2" t="n"/>
       <c r="R398" s="2" t="n"/>
       <c r="S398" s="2" t="n"/>
@@ -33863,10 +36779,18 @@
       <c r="L399" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M399" s="2" t="n"/>
+      <c r="M399" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N399" s="2" t="n"/>
       <c r="O399" s="2" t="n"/>
-      <c r="P399" s="2" t="n"/>
+      <c r="P399" s="2" t="inlineStr">
+        <is>
+          <t>Pano Koutrafas</t>
+        </is>
+      </c>
       <c r="Q399" s="2" t="n"/>
       <c r="R399" s="2" t="n"/>
       <c r="S399" s="2" t="n"/>
@@ -33947,10 +36871,18 @@
       <c r="L400" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M400" s="2" t="n"/>
+      <c r="M400" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N400" s="2" t="n"/>
       <c r="O400" s="2" t="n"/>
-      <c r="P400" s="2" t="n"/>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>Kidasi</t>
+        </is>
+      </c>
       <c r="Q400" s="2" t="n"/>
       <c r="R400" s="2" t="n"/>
       <c r="S400" s="2" t="n"/>
@@ -34031,10 +36963,18 @@
       <c r="L401" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M401" s="2" t="n"/>
+      <c r="M401" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N401" s="2" t="n"/>
       <c r="O401" s="2" t="n"/>
-      <c r="P401" s="2" t="n"/>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>Τέρρα</t>
+        </is>
+      </c>
       <c r="Q401" s="2" t="n"/>
       <c r="R401" s="2" t="n"/>
       <c r="S401" s="2" t="n"/>
@@ -34115,10 +37055,18 @@
       <c r="L402" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M402" s="2" t="n"/>
+      <c r="M402" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N402" s="2" t="n"/>
       <c r="O402" s="2" t="n"/>
-      <c r="P402" s="2" t="n"/>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>Anadiou</t>
+        </is>
+      </c>
       <c r="Q402" s="2" t="n"/>
       <c r="R402" s="2" t="n"/>
       <c r="S402" s="2" t="n"/>
@@ -34199,10 +37147,18 @@
       <c r="L403" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M403" s="2" t="n"/>
+      <c r="M403" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N403" s="2" t="n"/>
       <c r="O403" s="2" t="n"/>
-      <c r="P403" s="2" t="n"/>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>Kataliontas</t>
+        </is>
+      </c>
       <c r="Q403" s="2" t="n"/>
       <c r="R403" s="2" t="n"/>
       <c r="S403" s="2" t="n"/>
@@ -34283,10 +37239,18 @@
       <c r="L404" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M404" s="2" t="n"/>
+      <c r="M404" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N404" s="2" t="n"/>
       <c r="O404" s="2" t="n"/>
-      <c r="P404" s="2" t="n"/>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>Πάνω Πύργος</t>
+        </is>
+      </c>
       <c r="Q404" s="2" t="n"/>
       <c r="R404" s="2" t="n"/>
       <c r="S404" s="2" t="n"/>
@@ -34487,10 +37451,18 @@
       <c r="L407" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M407" s="2" t="n"/>
+      <c r="M407" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N407" s="2" t="n"/>
       <c r="O407" s="2" t="n"/>
-      <c r="P407" s="2" t="n"/>
+      <c r="P407" s="2" t="inlineStr">
+        <is>
+          <t>Kouka</t>
+        </is>
+      </c>
       <c r="Q407" s="2" t="n"/>
       <c r="R407" s="2" t="n"/>
       <c r="S407" s="2" t="n"/>
@@ -34571,10 +37543,18 @@
       <c r="L408" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M408" s="2" t="n"/>
+      <c r="M408" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N408" s="2" t="n"/>
       <c r="O408" s="2" t="n"/>
-      <c r="P408" s="2" t="n"/>
+      <c r="P408" s="2" t="inlineStr">
+        <is>
+          <t>Κοινότητα Παλαιόμυλου</t>
+        </is>
+      </c>
       <c r="Q408" s="2" t="n"/>
       <c r="R408" s="2" t="n"/>
       <c r="S408" s="2" t="n"/>
@@ -34715,10 +37695,18 @@
       <c r="L410" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M410" s="2" t="n"/>
+      <c r="M410" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N410" s="2" t="n"/>
       <c r="O410" s="2" t="n"/>
-      <c r="P410" s="2" t="n"/>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>Λουκρούνου</t>
+        </is>
+      </c>
       <c r="Q410" s="2" t="n"/>
       <c r="R410" s="2" t="n"/>
       <c r="S410" s="2" t="n"/>
@@ -34799,10 +37787,18 @@
       <c r="L411" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M411" s="2" t="n"/>
+      <c r="M411" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N411" s="2" t="n"/>
       <c r="O411" s="2" t="n"/>
-      <c r="P411" s="2" t="n"/>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>Petrofani</t>
+        </is>
+      </c>
       <c r="Q411" s="2" t="n"/>
       <c r="R411" s="2" t="n"/>
       <c r="S411" s="2" t="n"/>
@@ -34883,10 +37879,18 @@
       <c r="L412" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M412" s="2" t="n"/>
+      <c r="M412" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N412" s="2" t="n"/>
       <c r="O412" s="2" t="n"/>
-      <c r="P412" s="2" t="n"/>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>Μηλικούρι</t>
+        </is>
+      </c>
       <c r="Q412" s="2" t="n"/>
       <c r="R412" s="2" t="n"/>
       <c r="S412" s="2" t="n"/>
@@ -34967,10 +37971,18 @@
       <c r="L413" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M413" s="2" t="n"/>
+      <c r="M413" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N413" s="2" t="n"/>
       <c r="O413" s="2" t="n"/>
-      <c r="P413" s="2" t="n"/>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>Skouriotissa</t>
+        </is>
+      </c>
       <c r="Q413" s="2" t="n"/>
       <c r="R413" s="2" t="n"/>
       <c r="S413" s="2" t="n"/>
@@ -35051,10 +38063,18 @@
       <c r="L414" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M414" s="2" t="n"/>
+      <c r="M414" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N414" s="2" t="n"/>
       <c r="O414" s="2" t="n"/>
-      <c r="P414" s="2" t="n"/>
+      <c r="P414" s="2" t="inlineStr">
+        <is>
+          <t>Aplanta</t>
+        </is>
+      </c>
       <c r="Q414" s="2" t="n"/>
       <c r="R414" s="2" t="n"/>
       <c r="S414" s="2" t="n"/>
@@ -35135,10 +38155,18 @@
       <c r="L415" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M415" s="2" t="n"/>
+      <c r="M415" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N415" s="2" t="n"/>
       <c r="O415" s="2" t="n"/>
-      <c r="P415" s="2" t="n"/>
+      <c r="P415" s="2" t="inlineStr">
+        <is>
+          <t>Souskiou</t>
+        </is>
+      </c>
       <c r="Q415" s="2" t="n"/>
       <c r="R415" s="2" t="n"/>
       <c r="S415" s="2" t="n"/>
@@ -35219,10 +38247,18 @@
       <c r="L416" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M416" s="2" t="n"/>
+      <c r="M416" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N416" s="2" t="n"/>
       <c r="O416" s="2" t="n"/>
-      <c r="P416" s="2" t="n"/>
+      <c r="P416" s="2" t="inlineStr">
+        <is>
+          <t>Kissousa</t>
+        </is>
+      </c>
       <c r="Q416" s="2" t="n"/>
       <c r="R416" s="2" t="n"/>
       <c r="S416" s="2" t="n"/>
@@ -35303,10 +38339,18 @@
       <c r="L417" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M417" s="2" t="n"/>
+      <c r="M417" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N417" s="2" t="n"/>
       <c r="O417" s="2" t="n"/>
-      <c r="P417" s="2" t="n"/>
+      <c r="P417" s="2" t="inlineStr">
+        <is>
+          <t>Μανσούρα</t>
+        </is>
+      </c>
       <c r="Q417" s="2" t="n"/>
       <c r="R417" s="2" t="n"/>
       <c r="S417" s="2" t="n"/>
@@ -35387,10 +38431,18 @@
       <c r="L418" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M418" s="2" t="n"/>
+      <c r="M418" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N418" s="2" t="n"/>
       <c r="O418" s="2" t="n"/>
-      <c r="P418" s="2" t="n"/>
+      <c r="P418" s="2" t="inlineStr">
+        <is>
+          <t>Dörtyol</t>
+        </is>
+      </c>
       <c r="Q418" s="2" t="n"/>
       <c r="R418" s="2" t="n"/>
       <c r="S418" s="2" t="n"/>
@@ -35471,10 +38523,18 @@
       <c r="L419" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M419" s="2" t="n"/>
+      <c r="M419" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N419" s="2" t="n"/>
       <c r="O419" s="2" t="n"/>
-      <c r="P419" s="2" t="n"/>
+      <c r="P419" s="2" t="inlineStr">
+        <is>
+          <t>Alithinou</t>
+        </is>
+      </c>
       <c r="Q419" s="2" t="n"/>
       <c r="R419" s="2" t="n"/>
       <c r="S419" s="2" t="n"/>
@@ -35555,10 +38615,18 @@
       <c r="L420" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M420" s="2" t="n"/>
+      <c r="M420" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N420" s="2" t="n"/>
       <c r="O420" s="2" t="n"/>
-      <c r="P420" s="2" t="n"/>
+      <c r="P420" s="2" t="inlineStr">
+        <is>
+          <t>Kourdaka</t>
+        </is>
+      </c>
       <c r="Q420" s="2" t="n"/>
       <c r="R420" s="2" t="n"/>
       <c r="S420" s="2" t="n"/>
@@ -35639,10 +38707,18 @@
       <c r="L421" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M421" s="2" t="n"/>
+      <c r="M421" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N421" s="2" t="n"/>
       <c r="O421" s="2" t="n"/>
-      <c r="P421" s="2" t="n"/>
+      <c r="P421" s="2" t="inlineStr">
+        <is>
+          <t>Yıldırım</t>
+        </is>
+      </c>
       <c r="Q421" s="2" t="n"/>
       <c r="R421" s="2" t="n"/>
       <c r="S421" s="2" t="n"/>
@@ -35723,10 +38799,18 @@
       <c r="L422" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M422" s="2" t="n"/>
+      <c r="M422" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N422" s="2" t="n"/>
       <c r="O422" s="2" t="n"/>
-      <c r="P422" s="2" t="n"/>
+      <c r="P422" s="2" t="inlineStr">
+        <is>
+          <t>Agios Sozomenos</t>
+        </is>
+      </c>
       <c r="Q422" s="2" t="n"/>
       <c r="R422" s="2" t="n"/>
       <c r="S422" s="2" t="n"/>
@@ -35807,10 +38891,18 @@
       <c r="L423" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M423" s="2" t="n"/>
+      <c r="M423" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N423" s="2" t="n"/>
       <c r="O423" s="2" t="n"/>
-      <c r="P423" s="2" t="n"/>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>Καραμουλλήδες</t>
+        </is>
+      </c>
       <c r="Q423" s="2" t="n"/>
       <c r="R423" s="2" t="n"/>
       <c r="S423" s="2" t="n"/>
@@ -35891,10 +38983,18 @@
       <c r="L424" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M424" s="2" t="n"/>
+      <c r="M424" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N424" s="2" t="n"/>
       <c r="O424" s="2" t="n"/>
-      <c r="P424" s="2" t="n"/>
+      <c r="P424" s="2" t="inlineStr">
+        <is>
+          <t>Δήμος Λιβαδιών</t>
+        </is>
+      </c>
       <c r="Q424" s="2" t="n"/>
       <c r="R424" s="2" t="n"/>
       <c r="S424" s="2" t="n"/>
@@ -35975,10 +39075,18 @@
       <c r="L425" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M425" s="2" t="n"/>
+      <c r="M425" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N425" s="2" t="n"/>
       <c r="O425" s="2" t="n"/>
-      <c r="P425" s="2" t="n"/>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>Faleia</t>
+        </is>
+      </c>
       <c r="Q425" s="2" t="n"/>
       <c r="R425" s="2" t="n"/>
       <c r="S425" s="2" t="n"/>
@@ -36059,10 +39167,18 @@
       <c r="L426" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M426" s="2" t="n"/>
+      <c r="M426" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N426" s="2" t="n"/>
       <c r="O426" s="2" t="n"/>
-      <c r="P426" s="2" t="n"/>
+      <c r="P426" s="2" t="inlineStr">
+        <is>
+          <t>Mamountali</t>
+        </is>
+      </c>
       <c r="Q426" s="2" t="n"/>
       <c r="R426" s="2" t="n"/>
       <c r="S426" s="2" t="n"/>
@@ -36143,10 +39259,18 @@
       <c r="L427" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M427" s="2" t="n"/>
+      <c r="M427" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N427" s="2" t="n"/>
       <c r="O427" s="2" t="n"/>
-      <c r="P427" s="2" t="n"/>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>Mousere</t>
+        </is>
+      </c>
       <c r="Q427" s="2" t="n"/>
       <c r="R427" s="2" t="n"/>
       <c r="S427" s="2" t="n"/>
@@ -36227,10 +39351,18 @@
       <c r="L428" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="M428" s="2" t="n"/>
+      <c r="M428" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N428" s="2" t="n"/>
       <c r="O428" s="2" t="n"/>
-      <c r="P428" s="2" t="n"/>
+      <c r="P428" s="2" t="inlineStr">
+        <is>
+          <t>Βίκλα</t>
+        </is>
+      </c>
       <c r="Q428" s="2" t="n"/>
       <c r="R428" s="2" t="n"/>
       <c r="S428" s="2" t="n"/>
